--- a/week2/SQE_Lab2.xlsx
+++ b/week2/SQE_Lab2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ABDUR REHMAN\Documents\Assignment 6 sem\SQE Lab\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ABDUR REHMAN\Documents\Assignment 6 sem\SQE Lab\sqe-lab-abdurrehman\week2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F81B7AF8-7D58-452F-B91B-9FBCD3F8B602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD7DF8B-AFD1-472A-9F74-B436BA4B39F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📋 Session Setup" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1173" uniqueCount="673">
   <si>
     <t>SQE Lab Session 2 — ISO 25010 Quality Attribute Analysis</t>
   </si>
@@ -833,74 +833,34 @@
     <t>15%</t>
   </si>
   <si>
-    <t>[Hint: Does the app deliver all expected features correctly and completely? Test all advertised functions. Note any missing/broken features.]
-Observation 1:
-Observation 2:</t>
-  </si>
-  <si>
     <t>2. Performance Efficiency</t>
   </si>
   <si>
     <t>12%</t>
   </si>
   <si>
-    <t>[Hint: Response time, loading speed, battery &amp; data usage. Record actual timings in seconds for at least 3 operations.]
-Observation 1:
-Observation 2:</t>
-  </si>
-  <si>
     <t>3. Compatibility</t>
   </si>
   <si>
     <t>10%</t>
   </si>
   <si>
-    <t>[Hint: Works correctly on different OS versions, screen sizes, browsers? Check platform availability listing. Test sharing.]
-Observation 1:
-Observation 2:</t>
-  </si>
-  <si>
     <t>4. Usability</t>
   </si>
   <si>
-    <t>[Hint: Ease of navigation, clarity of UI, onboarding experience? Complete 5 timed tasks without guidance.]
-Observation 1:
-Observation 2:</t>
-  </si>
-  <si>
     <t>5. Reliability</t>
   </si>
   <si>
-    <t>[Hint: App crashes, error handling, offline behavior, data integrity? Test Airplane Mode. Force-close mid-task.]
-Observation 1:
-Observation 2:</t>
-  </si>
-  <si>
     <t>6. Security</t>
   </si>
   <si>
-    <t>[Hint: Login security, data privacy, permissions, encryption? Check 2FA, permissions list, privacy policy, lockout behavior.]
-Observation 1:
-Observation 2:</t>
-  </si>
-  <si>
     <t>7. Maintainability</t>
   </si>
   <si>
     <t>8%</t>
   </si>
   <si>
-    <t>[Hint: Update frequency, bug fix speed, changelog quality? Review app store update history &amp; release notes.]
-Observation 1:
-Observation 2:</t>
-  </si>
-  <si>
     <t>8. Portability</t>
-  </si>
-  <si>
-    <t>[Hint: Available on multiple platforms, cross-device sync? Test install/uninstall. Check dark mode &amp; accessibility sync.]
-Observation 1:
-Observation 2:</t>
   </si>
   <si>
     <t>WEIGHTED TOTAL SCORE (out of 5.00)</t>
@@ -2017,6 +1977,118 @@
   </si>
   <si>
     <t>Based on the analysis, the choice between the two applications depends on user priorities. Safari is recommended for users who value high performance, strong security, and reliable operation, particularly within optimized environments. However, Chrome is recommended for users who require a more versatile, user-friendly, and maintainable solution that performs consistently across different platforms. From a balanced ISO 25010 perspective, Chrome provides a more uniform quality distribution, while Safari is ideal for performance-focused scenarios. Therefore, for general-purpose use, Chrome is slightly more suitable, whereas Safari is preferable in performance-critical contexts.</t>
+  </si>
+  <si>
+    <t>Observation 1: Primary core function passed — opened a website normally without any issues. All tested features (bookmarks, incognito mode) function correctly.
+Observation 2: Error handling is robust — Chrome displays security warnings for non-HTTPS websites and shows "no internet connection" message when offline. Edge case with 15-20 tabs caused lag and slow switching, indicating partial performance under extreme load.</t>
+  </si>
+  <si>
+    <t>Observation 1: Cold start time measured at 2.4 seconds (target &lt;3 seconds). First website loaded in 1.3 seconds. Image loading took 2 seconds.
+Observation 2: On slow 4G network, website loaded in 10.25 seconds (exceeds &lt;5 second target). Battery drain was excellent at 1% over 10 minutes. Data usage was 5MB in 10 minutes (under 10MB target).</t>
+  </si>
+  <si>
+    <t>Observation 1: Chrome is available on all platforms (Android, iOS, Windows, macOS, Web, Linux). Cross-device sync works seamlessly — browsing history from laptop appears on mobile.
+Observation 2: Supports dark mode that respects OS settings. Content sharing works both directions — can receive shares from other apps and share downloaded files to 3+ apps. No features broken on Android 13.5.0.</t>
+  </si>
+  <si>
+    <t>Observation 1: Usability tasks completed without errors: change core setting (10 sec), primary function first time (2 sec), find help section (5 sec), share content (15 sec), delete item (5 sec).
+Observation 2: Error messages are clear and actionable. Visual hierarchy effectively prioritizes important information. Accessibility supports large text and screen readers. No onboarding tutorial for new users.</t>
+  </si>
+  <si>
+    <t>Observation 1: No crashes during 10-minute continuous use. Airplane Mode test showed graceful handling with "no internet connection" message. Reconnect recovery successfully synced data after connectivity restored.
+Observation 2: Force-close mid-task partially saves progress — tabs are restored but reload content. Server error messages are meaningful ("Server Not found").</t>
+  </si>
+  <si>
+    <t>Observation 1: Uses HTTPS with padlock indicator. Permissions are justified for app purpose. 2FA/biometric login available in settings (Google account integration).
+Observation 2: Privacy policy clearly documents data collection practices. Login lockout activates after 3 incorrect attempts. Missing auto-lock on inactivity — app stays open indefinitely.</t>
+  </si>
+  <si>
+    <t>Observation 1: Updates released weekly on Play Store. Changelog clearly documents bug fixes with specific details.
+Observation 2: No widespread long-standing unfixed bugs in app store reviews. Public bug tracker/feedback channel exists for user reporting.</t>
+  </si>
+  <si>
+    <t>Observation 1: Available on all major platforms (Android, iOS, Windows, macOS, Web, Linux). Installation and uninstallation process is clean with no residual files observed.
+Observation 2: Cross-device data syncworks automatically when signed into Google account. Respects system accessibility settings including font size and dark mode.</t>
+  </si>
+  <si>
+    <t>Observation 1: Primary core function passed — opened website normally with no issues. Secondary features (bookmarks, private mode) all function correctly without problems.
+Observation 2: Error handling is excellent — Safari displays security warnings for non-HTTPS websites and clear "no internet connection" messages. Edge case with multiple tabs opened without lag — handled 15-20 tabs smoothly with no performance degradation.</t>
+  </si>
+  <si>
+    <t>Observation 1: Cold start time very fast at 1.5 seconds (target &lt;3 seconds). Website loading took 4.4 seconds (exceeds &lt;1 second target). Image loading completed in 1.9 seconds.
+Observation 2: Battery drain excellent at 1% over 10 minutes. Slow network (4G) performance was weak at 15 seconds for page load (exceeds &lt;5 second target). Data usage higher than Chrome at 20MB in 10 minutes (exceeds 10MB target).</t>
+  </si>
+  <si>
+    <t>Observation 1: Limited platform availability — only iOS and macOS (no Android, Windows, or Linux support). Cross-device sync works via iCloud.
+Observation 2: Content sharing works both directions. Dark mode respects OS settings. No features broken on iOS 26.4.1. Platform restriction significantly limits compatibility compared to cross-platform browsers.</t>
+  </si>
+  <si>
+    <t>Observation 1: Tasks completed: change core setting (20 sec), primary function first time (4 sec), share content (3 sec), delete item (2 sec). Help/Support section not found (0 sec, incomplete).
+Observation 2: Error messages are clear and helpful. Visual hierarchy is well-designed. No onboarding tutorial. Accessibility does NOT support large text, high contrast, or screen reader — significant deficiency for users with disabilities.</t>
+  </si>
+  <si>
+    <t>Observation 1: No crashes during 10-minute continuous use. Airplane Mode test showed graceful handling with appropriate error messaging. Reconnect recovery successfully restored functionality.
+Observation 2: Force-close mid-task preserves progress — tabs restored and content reloads. Server error messages are meaningful. Overall reliability is excellent with no observed failures.</t>
+  </si>
+  <si>
+    <t>Observation 1: Uses HTTPS with padlock indicator. Permissions are justified for app purpose. Privacy policy clearly documents data collection practices (Apple's privacy-focused approach).
+Observation 2: Auto-lock on inactivity NOT available. Login lockout does NOT activate after 3 incorrect attempts (no account lockout mechanism observed). 2FA/biometric NOT available for browser itself (relies on iCloud Keychain separately).</t>
+  </si>
+  <si>
+    <t>Observation 1: Updates released monthly — slower frequency than competitors (Chrome weekly). Changelog quality is good with documented bug fixes.
+Observation 2: No public bug tracker or feedback channel for users to report issues directly. CVE response history not clearly documented for this specific app. Lower maintainability due to closed ecosystem and opaque development process.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Observation 1: Platform support limited to iOS and macOS only — not available on Android, Windows, or Linux. Installation/uninstallation process is clean.
+Observation 2: Cross-device data sync works via iCloud across Apple devices. Respects system accessibility settings (font size, dark mode). Lower portability score due to Apple ecosystem lock-in.</t>
+  </si>
+  <si>
+    <t>Implement aggressive tab freezing and memory compression for background tabs</t>
+  </si>
+  <si>
+    <t>Opening 15-20 tabs simultaneously caused significant lag, slow switching between tabs, and general interface stuttering. The browser struggles to maintain smooth performance under multi-tab workload.</t>
+  </si>
+  <si>
+    <t>Users could keep 20+ tabs open without experiencing lag, enabling seamless multitasking between research, shopping, and social media tabs without performance degradation.</t>
+  </si>
+  <si>
+    <t>Chrome Mobile should implement aggressive tab freezing and memory compression for background tabs in order to improve Performance Efficiency from its current rating of 4 to a target of 5. Currently, opening 15-20 tabs simultaneously causes significant lag, slow switching between tabs, and general interface stuttering, as documented during edge case testing. This change would benefit users by allowing them to keep 20+ tabs open without experiencing lag, enabling seamless multitasking between research, shopping, and social media tabs without performance degradation.</t>
+  </si>
+  <si>
+    <t>Add an auto-lock timeout feature that locks the browser after user-specified period of inactivity (30 seconds to 5 minutes)</t>
+  </si>
+  <si>
+    <t>Chrome stays open indefinitely with no auto-lock mechanism. If a user walks away from their device while logged into sensitive accounts (banking, email, social media), anyone can access all open tabs and saved passwords.</t>
+  </si>
+  <si>
+    <t>Users would have peace of mind knowing their browsing session automatically locks after inactivity, protecting sensitive personal data, saved passwords, and logged-in accounts from unauthorized access on shared or lost devices.</t>
+  </si>
+  <si>
+    <t>Chrome Mobile should add an auto-lock timeout feature that locks the browser after a user-specified period of inactivity (30 seconds to 5 minutes) in order to improve Security from its current rating of 4 to a target of 5. Currently, Chrome stays open indefinitely with no auto-lock mechanism — if a user walks away from their device while logged into sensitive accounts (banking, email, social media), anyone can access all open tabs and saved passwords. This change would benefit users by providing peace of mind knowing their browsing session automatically locks after inactivity, protecting sensitive personal data, saved passwords, and logged-in accounts from unauthorized access on shared or lost devices.</t>
+  </si>
+  <si>
+    <t>Expand platform availability by releasing a Windows desktop version and an Android mobile version</t>
+  </si>
+  <si>
+    <t>Safari is exclusively available only on iOS and macOS platforms. Users on Windows PCs, Android phones, or Linux computers cannot access Safari, forcing them to switch browsers when moving between Apple and non-Apple devices.</t>
+  </si>
+  <si>
+    <t>Users could maintain a consistent browsing experience with synchronized bookmarks, history, and passwords across ALL their devices regardless of platform, eliminating the friction of switching between different browsers on Windows or Android.</t>
+  </si>
+  <si>
+    <t>Safari should expand platform availability by releasing a Windows desktop version and an Android mobile version in order to improve Compatibility from its current rating of 3.5 to a target of 5. Currently, Safari is exclusively available only on iOS and macOS platforms — users on Windows PCs, Android phones, or Linux computers cannot access Safari, forcing them to switch browsers when moving between Apple and non-Apple devices. This change would benefit users by allowing them to maintain a consistent browsing experience with synchronized bookmarks, history, and passwords across ALL their devices regardless of platform, eliminating the friction of switching between different browsers on Windows or Android.</t>
+  </si>
+  <si>
+    <t>Introduce a public bug tracker or feedback portal where users can report issues, vote on existing bugs, and track resolution status</t>
+  </si>
+  <si>
+    <t>Safari has no public bug tracker or transparent feedback channel. Users cannot see which bugs Apple has acknowledged, view workarounds, or track when fixes will arrive. The development process is entirely opaque to end users.</t>
+  </si>
+  <si>
+    <t>Users could report bugs directly, see if issues are already known, receive updates on fix progress, and access workarounds from the community, leading to faster bug resolution and a more transparent development relationship with Apple.</t>
+  </si>
+  <si>
+    <t>Safari should introduce a public bug tracker or feedback portal where users can report issues, vote on existing bugs, and track resolution status in order to improve Maintainability from its current rating of 3 to a target of 5. Currently, Safari has no public bug tracker or transparent feedback channel — users cannot see which bugs Apple has acknowledged, view workarounds, or track when fixes will arrive, as the development process is entirely opaque to end users. This change would benefit users by allowing them to report bugs directly, see if issues are already known, receive updates on fix progress, and access workarounds from the community, leading to faster bug resolution and a more transparent development relationship with Apple.</t>
   </si>
 </sst>
 </file>
@@ -2702,6 +2774,21 @@
     <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2714,23 +2801,32 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2741,79 +2837,55 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="18" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3093,36 +3165,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="108" t="s">
+      <c r="B1" s="113" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
     </row>
     <row r="2" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="114" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="109"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
     </row>
     <row r="3" spans="2:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="107" t="s">
+      <c r="B4" s="112" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="107"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
     </row>
     <row r="5" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -3132,7 +3204,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -3152,7 +3224,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -3162,10 +3234,10 @@
         <v>7</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="E9" s="4"/>
     </row>
@@ -3174,10 +3246,10 @@
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="E10" s="4"/>
     </row>
@@ -3186,27 +3258,27 @@
         <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
     </row>
     <row r="12" spans="2:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="13" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="107" t="s">
+      <c r="B13" s="112" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="107"/>
-      <c r="D13" s="107"/>
-      <c r="E13" s="107"/>
+      <c r="C13" s="112"/>
+      <c r="D13" s="112"/>
+      <c r="E13" s="112"/>
     </row>
     <row r="14" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="110" t="s">
+      <c r="B14" s="115" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="110"/>
-      <c r="E14" s="110"/>
+      <c r="C14" s="115"/>
+      <c r="D14" s="115"/>
+      <c r="E14" s="115"/>
     </row>
     <row r="15" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="1" t="s">
@@ -3308,12 +3380,12 @@
     </row>
     <row r="22" spans="2:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="23" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="107" t="s">
+      <c r="B23" s="112" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="107"/>
-      <c r="D23" s="107"/>
-      <c r="E23" s="107"/>
+      <c r="C23" s="112"/>
+      <c r="D23" s="112"/>
+      <c r="E23" s="112"/>
     </row>
     <row r="24" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="2" t="s">
@@ -3341,12 +3413,12 @@
     </row>
     <row r="26" spans="2:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="27" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="107" t="s">
+      <c r="B27" s="112" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="107"/>
-      <c r="D27" s="107"/>
-      <c r="E27" s="107"/>
+      <c r="C27" s="112"/>
+      <c r="D27" s="112"/>
+      <c r="E27" s="112"/>
     </row>
     <row r="28" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="17" t="s">
@@ -3380,8 +3452,8 @@
       <c r="B30" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="144" t="s">
-        <v>565</v>
+      <c r="C30" s="111" t="s">
+        <v>557</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>47</v>
@@ -3395,13 +3467,13 @@
         <v>48</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>48</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
     </row>
     <row r="32" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -3437,7 +3509,7 @@
         <v>51</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>51</v>
@@ -3446,12 +3518,12 @@
     </row>
     <row r="35" spans="2:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="36" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="107" t="s">
+      <c r="B36" s="112" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="107"/>
-      <c r="D36" s="107"/>
-      <c r="E36" s="107"/>
+      <c r="C36" s="112"/>
+      <c r="D36" s="112"/>
+      <c r="E36" s="112"/>
     </row>
     <row r="37" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B37" s="18" t="s">
@@ -3541,12 +3613,12 @@
     </row>
     <row r="44" spans="2:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="45" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="107" t="s">
+      <c r="B45" s="112" t="s">
         <v>71</v>
       </c>
-      <c r="C45" s="107"/>
-      <c r="D45" s="107"/>
-      <c r="E45" s="107"/>
+      <c r="C45" s="112"/>
+      <c r="D45" s="112"/>
+      <c r="E45" s="112"/>
     </row>
     <row r="46" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="18" t="s">
@@ -3664,14 +3736,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="115" t="s">
-        <v>504</v>
-      </c>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
+      <c r="B1" s="116" t="s">
+        <v>496</v>
+      </c>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
     </row>
     <row r="2" spans="2:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3679,19 +3751,19 @@
         <v>53</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="F3" s="18" t="s">
         <v>256</v>
       </c>
       <c r="G3" s="18" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="42" customHeight="1" x14ac:dyDescent="0.35">
@@ -3699,19 +3771,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="82" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="D4" s="83" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="F4" s="84" t="s">
         <v>260</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
     </row>
     <row r="5" spans="2:7" ht="42" customHeight="1" x14ac:dyDescent="0.35">
@@ -3719,19 +3791,19 @@
         <v>2</v>
       </c>
       <c r="C5" s="86" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="D5" s="87" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="F5" s="88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
     </row>
     <row r="6" spans="2:7" ht="42" customHeight="1" x14ac:dyDescent="0.35">
@@ -3739,19 +3811,19 @@
         <v>3</v>
       </c>
       <c r="C6" s="90" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="D6" s="91" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="E6" s="74" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="F6" s="92" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
     </row>
     <row r="7" spans="2:7" ht="42" customHeight="1" x14ac:dyDescent="0.35">
@@ -3759,19 +3831,19 @@
         <v>4</v>
       </c>
       <c r="C7" s="93" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="D7" s="94" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="F7" s="95" t="s">
         <v>260</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="42" customHeight="1" x14ac:dyDescent="0.35">
@@ -3779,19 +3851,19 @@
         <v>5</v>
       </c>
       <c r="C8" s="97" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="D8" s="98" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="F8" s="63" t="s">
         <v>260</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="42" customHeight="1" x14ac:dyDescent="0.35">
@@ -3799,19 +3871,19 @@
         <v>6</v>
       </c>
       <c r="C9" s="100" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="D9" s="101" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="F9" s="102" t="s">
         <v>260</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="42" customHeight="1" x14ac:dyDescent="0.35">
@@ -3819,19 +3891,19 @@
         <v>7</v>
       </c>
       <c r="C10" s="86" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="D10" s="87" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="F10" s="88" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="G10" s="19" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="42" customHeight="1" x14ac:dyDescent="0.35">
@@ -3839,112 +3911,112 @@
         <v>8</v>
       </c>
       <c r="C11" s="82" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="D11" s="83" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="F11" s="84" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="13" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="107" t="s">
-        <v>538</v>
-      </c>
-      <c r="C13" s="107"/>
-      <c r="D13" s="107"/>
-      <c r="E13" s="107"/>
-      <c r="F13" s="107"/>
-      <c r="G13" s="107"/>
+      <c r="B13" s="112" t="s">
+        <v>530</v>
+      </c>
+      <c r="C13" s="112"/>
+      <c r="D13" s="112"/>
+      <c r="E13" s="112"/>
+      <c r="F13" s="112"/>
+      <c r="G13" s="112"/>
     </row>
     <row r="14" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="17" t="s">
-        <v>539</v>
-      </c>
-      <c r="C14" s="119" t="s">
-        <v>540</v>
-      </c>
-      <c r="D14" s="119"/>
-      <c r="E14" s="119"/>
-      <c r="F14" s="119" t="s">
-        <v>541</v>
-      </c>
-      <c r="G14" s="119"/>
+        <v>531</v>
+      </c>
+      <c r="C14" s="127" t="s">
+        <v>532</v>
+      </c>
+      <c r="D14" s="127"/>
+      <c r="E14" s="127"/>
+      <c r="F14" s="127" t="s">
+        <v>533</v>
+      </c>
+      <c r="G14" s="127"/>
     </row>
     <row r="15" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="24" t="s">
-        <v>542</v>
-      </c>
-      <c r="C15" s="118" t="s">
-        <v>543</v>
-      </c>
-      <c r="D15" s="118"/>
-      <c r="E15" s="118"/>
-      <c r="F15" s="137" t="s">
-        <v>544</v>
-      </c>
-      <c r="G15" s="137"/>
+        <v>534</v>
+      </c>
+      <c r="C15" s="126" t="s">
+        <v>535</v>
+      </c>
+      <c r="D15" s="126"/>
+      <c r="E15" s="126"/>
+      <c r="F15" s="143" t="s">
+        <v>536</v>
+      </c>
+      <c r="G15" s="143"/>
     </row>
     <row r="16" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="24" t="s">
-        <v>545</v>
-      </c>
-      <c r="C16" s="117" t="s">
-        <v>546</v>
-      </c>
-      <c r="D16" s="117"/>
-      <c r="E16" s="117"/>
-      <c r="F16" s="137" t="s">
-        <v>547</v>
-      </c>
-      <c r="G16" s="137"/>
+        <v>537</v>
+      </c>
+      <c r="C16" s="125" t="s">
+        <v>538</v>
+      </c>
+      <c r="D16" s="125"/>
+      <c r="E16" s="125"/>
+      <c r="F16" s="143" t="s">
+        <v>539</v>
+      </c>
+      <c r="G16" s="143"/>
     </row>
     <row r="17" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="24" t="s">
-        <v>548</v>
-      </c>
-      <c r="C17" s="118" t="s">
-        <v>549</v>
-      </c>
-      <c r="D17" s="118"/>
-      <c r="E17" s="118"/>
-      <c r="F17" s="137" t="s">
-        <v>550</v>
-      </c>
-      <c r="G17" s="137"/>
+        <v>540</v>
+      </c>
+      <c r="C17" s="126" t="s">
+        <v>541</v>
+      </c>
+      <c r="D17" s="126"/>
+      <c r="E17" s="126"/>
+      <c r="F17" s="143" t="s">
+        <v>542</v>
+      </c>
+      <c r="G17" s="143"/>
     </row>
     <row r="18" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="24" t="s">
-        <v>551</v>
-      </c>
-      <c r="C18" s="117" t="s">
-        <v>552</v>
-      </c>
-      <c r="D18" s="117"/>
-      <c r="E18" s="117"/>
-      <c r="F18" s="137" t="s">
-        <v>553</v>
-      </c>
-      <c r="G18" s="137"/>
+        <v>543</v>
+      </c>
+      <c r="C18" s="125" t="s">
+        <v>544</v>
+      </c>
+      <c r="D18" s="125"/>
+      <c r="E18" s="125"/>
+      <c r="F18" s="143" t="s">
+        <v>545</v>
+      </c>
+      <c r="G18" s="143"/>
     </row>
     <row r="19" spans="2:7" ht="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="20" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="107" t="s">
-        <v>554</v>
-      </c>
-      <c r="C20" s="107"/>
-      <c r="D20" s="107"/>
-      <c r="E20" s="107"/>
-      <c r="F20" s="107"/>
-      <c r="G20" s="107"/>
+      <c r="B20" s="112" t="s">
+        <v>546</v>
+      </c>
+      <c r="C20" s="112"/>
+      <c r="D20" s="112"/>
+      <c r="E20" s="112"/>
+      <c r="F20" s="112"/>
+      <c r="G20" s="112"/>
     </row>
     <row r="21" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="18" t="s">
@@ -3953,14 +4025,14 @@
       <c r="C21" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="D21" s="130" t="s">
+      <c r="D21" s="142" t="s">
         <v>74</v>
       </c>
-      <c r="E21" s="130"/>
-      <c r="F21" s="130" t="s">
-        <v>555</v>
-      </c>
-      <c r="G21" s="130"/>
+      <c r="E21" s="142"/>
+      <c r="F21" s="142" t="s">
+        <v>547</v>
+      </c>
+      <c r="G21" s="142"/>
     </row>
     <row r="22" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="103">
@@ -3969,14 +4041,14 @@
       <c r="C22" s="76" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="131" t="s">
+      <c r="D22" s="137" t="s">
         <v>77</v>
       </c>
-      <c r="E22" s="131"/>
-      <c r="F22" s="136" t="s">
+      <c r="E22" s="137"/>
+      <c r="F22" s="144" t="s">
         <v>78</v>
       </c>
-      <c r="G22" s="136"/>
+      <c r="G22" s="144"/>
     </row>
     <row r="23" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="104">
@@ -3985,14 +4057,14 @@
       <c r="C23" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="D23" s="132" t="s">
+      <c r="D23" s="138" t="s">
         <v>80</v>
       </c>
-      <c r="E23" s="132"/>
-      <c r="F23" s="136" t="s">
+      <c r="E23" s="138"/>
+      <c r="F23" s="144" t="s">
         <v>81</v>
       </c>
-      <c r="G23" s="136"/>
+      <c r="G23" s="144"/>
     </row>
     <row r="24" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="44">
@@ -4001,14 +4073,14 @@
       <c r="C24" s="78" t="s">
         <v>82</v>
       </c>
-      <c r="D24" s="133" t="s">
+      <c r="D24" s="139" t="s">
         <v>83</v>
       </c>
-      <c r="E24" s="133"/>
-      <c r="F24" s="136" t="s">
+      <c r="E24" s="139"/>
+      <c r="F24" s="144" t="s">
         <v>84</v>
       </c>
-      <c r="G24" s="136"/>
+      <c r="G24" s="144"/>
     </row>
     <row r="25" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="105">
@@ -4017,14 +4089,14 @@
       <c r="C25" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="D25" s="134" t="s">
+      <c r="D25" s="140" t="s">
         <v>86</v>
       </c>
-      <c r="E25" s="134"/>
-      <c r="F25" s="136" t="s">
+      <c r="E25" s="140"/>
+      <c r="F25" s="144" t="s">
         <v>87</v>
       </c>
-      <c r="G25" s="136"/>
+      <c r="G25" s="144"/>
     </row>
     <row r="26" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="106">
@@ -4033,34 +4105,17 @@
       <c r="C26" s="80" t="s">
         <v>88</v>
       </c>
-      <c r="D26" s="129" t="s">
+      <c r="D26" s="141" t="s">
         <v>89</v>
       </c>
-      <c r="E26" s="129"/>
-      <c r="F26" s="136" t="s">
+      <c r="E26" s="141"/>
+      <c r="F26" s="144" t="s">
         <v>90</v>
       </c>
-      <c r="G26" s="136"/>
+      <c r="G26" s="144"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="B20:G20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
     <mergeCell ref="D26:E26"/>
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="D23:E23"/>
@@ -4069,6 +4124,23 @@
     <mergeCell ref="F24:G24"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:G25"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="F15:G15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -4088,111 +4160,111 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="115" t="s">
+      <c r="B1" s="116" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
     </row>
     <row r="2" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="117" t="s">
         <v>92</v>
       </c>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
     </row>
     <row r="3" spans="2:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="107" t="s">
+      <c r="B4" s="112" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="107"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
     </row>
     <row r="5" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="114" t="str">
+      <c r="C5" s="118" t="str">
         <f>'📋 Session Setup'!C29</f>
         <v>Chrome Mobile</v>
       </c>
-      <c r="D5" s="114"/>
-      <c r="E5" s="114"/>
-      <c r="F5" s="114"/>
+      <c r="D5" s="118"/>
+      <c r="E5" s="118"/>
+      <c r="F5" s="118"/>
     </row>
     <row r="6" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="114" t="str">
+      <c r="C6" s="118" t="str">
         <f>'📋 Session Setup'!C30</f>
         <v>147.0.7727.101</v>
       </c>
-      <c r="D6" s="114"/>
-      <c r="E6" s="114"/>
-      <c r="F6" s="114"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="118"/>
     </row>
     <row r="7" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="114" t="str">
+      <c r="C7" s="118" t="str">
         <f>'📋 Session Setup'!C9</f>
         <v>iPhone 17 Pro Max</v>
       </c>
-      <c r="D7" s="114"/>
-      <c r="E7" s="114"/>
-      <c r="F7" s="114"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
     </row>
     <row r="8" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="114" t="s">
-        <v>569</v>
-      </c>
-      <c r="D8" s="114"/>
-      <c r="E8" s="114"/>
-      <c r="F8" s="114"/>
+      <c r="C8" s="118" t="s">
+        <v>561</v>
+      </c>
+      <c r="D8" s="118"/>
+      <c r="E8" s="118"/>
+      <c r="F8" s="118"/>
     </row>
     <row r="9" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C9" s="114" t="s">
-        <v>570</v>
-      </c>
-      <c r="D9" s="114"/>
-      <c r="E9" s="114"/>
-      <c r="F9" s="114"/>
+      <c r="C9" s="118" t="s">
+        <v>562</v>
+      </c>
+      <c r="D9" s="118"/>
+      <c r="E9" s="118"/>
+      <c r="F9" s="118"/>
     </row>
     <row r="10" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C10" s="138">
+      <c r="C10" s="119">
         <v>0.60277777777777775</v>
       </c>
-      <c r="D10" s="114"/>
-      <c r="E10" s="114"/>
-      <c r="F10" s="114"/>
+      <c r="D10" s="118"/>
+      <c r="E10" s="118"/>
+      <c r="F10" s="118"/>
     </row>
     <row r="11" spans="2:6" ht="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="107" t="s">
+      <c r="B12" s="112" t="s">
         <v>96</v>
       </c>
-      <c r="C12" s="107"/>
-      <c r="D12" s="107"/>
-      <c r="E12" s="107"/>
-      <c r="F12" s="107"/>
+      <c r="C12" s="112"/>
+      <c r="D12" s="112"/>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
     </row>
     <row r="13" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="1" t="s">
@@ -4219,12 +4291,12 @@
         <v>103</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>572</v>
-      </c>
-      <c r="F14" s="139"/>
+        <v>564</v>
+      </c>
+      <c r="F14" s="107"/>
     </row>
     <row r="15" spans="2:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="33" t="s">
@@ -4234,10 +4306,10 @@
         <v>105</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="F15" s="32"/>
     </row>
@@ -4249,10 +4321,10 @@
         <v>107</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="F16" s="32"/>
     </row>
@@ -4264,10 +4336,10 @@
         <v>109</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="E17" s="32" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="F17" s="32"/>
     </row>
@@ -4279,19 +4351,19 @@
         <v>111</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="F18" s="32"/>
     </row>
     <row r="19" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="113" t="s">
+      <c r="B19" s="120" t="s">
         <v>112</v>
       </c>
-      <c r="C19" s="113"/>
-      <c r="D19" s="113"/>
+      <c r="C19" s="120"/>
+      <c r="D19" s="120"/>
       <c r="E19" s="34">
         <v>4.5</v>
       </c>
@@ -4301,13 +4373,13 @@
     </row>
     <row r="20" spans="2:6" ht="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="21" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="107" t="s">
+      <c r="B21" s="112" t="s">
         <v>114</v>
       </c>
-      <c r="C21" s="107"/>
-      <c r="D21" s="107"/>
-      <c r="E21" s="107"/>
-      <c r="F21" s="107"/>
+      <c r="C21" s="112"/>
+      <c r="D21" s="112"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
     </row>
     <row r="22" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="1" t="s">
@@ -4334,13 +4406,13 @@
         <v>120</v>
       </c>
       <c r="D23" s="25" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="E23" s="31" t="s">
         <v>121</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
     </row>
     <row r="24" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -4351,13 +4423,13 @@
         <v>123</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="E24" s="19" t="s">
         <v>124</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
     </row>
     <row r="25" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -4368,13 +4440,13 @@
         <v>126</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="E25" s="31" t="s">
         <v>127</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="26" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -4384,14 +4456,14 @@
       <c r="C26" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="D26" s="140">
+      <c r="D26" s="108">
         <v>0.01</v>
       </c>
       <c r="E26" s="19" t="s">
         <v>130</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
     </row>
     <row r="27" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -4402,13 +4474,13 @@
         <v>132</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="E27" s="31" t="s">
         <v>133</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
     </row>
     <row r="28" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -4419,7 +4491,7 @@
         <v>135</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="E28" s="19" t="s">
         <v>136</v>
@@ -4427,11 +4499,11 @@
       <c r="F28" s="25"/>
     </row>
     <row r="29" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="113" t="s">
+      <c r="B29" s="120" t="s">
         <v>137</v>
       </c>
-      <c r="C29" s="113"/>
-      <c r="D29" s="113"/>
+      <c r="C29" s="120"/>
+      <c r="D29" s="120"/>
       <c r="E29" s="34">
         <v>4</v>
       </c>
@@ -4441,13 +4513,13 @@
     </row>
     <row r="30" spans="2:6" ht="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="31" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="107" t="s">
+      <c r="B31" s="112" t="s">
         <v>138</v>
       </c>
-      <c r="C31" s="107"/>
-      <c r="D31" s="107"/>
-      <c r="E31" s="107"/>
-      <c r="F31" s="107"/>
+      <c r="C31" s="112"/>
+      <c r="D31" s="112"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
     </row>
     <row r="32" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="1" t="s">
@@ -4477,10 +4549,10 @@
         <v>10</v>
       </c>
       <c r="E33" s="25" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="F33" s="25" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
     </row>
     <row r="34" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -4491,13 +4563,13 @@
         <v>146</v>
       </c>
       <c r="D34" s="25" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="E34" s="25" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="F34" s="25" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
     </row>
     <row r="35" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -4508,13 +4580,13 @@
         <v>148</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E35" s="25" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="F35" s="25" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
     </row>
     <row r="36" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -4525,13 +4597,13 @@
         <v>150</v>
       </c>
       <c r="D36" s="25" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E36" s="25" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="F36" s="25" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
     </row>
     <row r="37" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -4542,13 +4614,13 @@
         <v>152</v>
       </c>
       <c r="D37" s="25" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E37" s="25" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="F37" s="25" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
     </row>
     <row r="38" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -4559,13 +4631,13 @@
         <v>154</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E38" s="25" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="F38" s="25" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
     </row>
     <row r="39" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -4576,21 +4648,21 @@
         <v>156</v>
       </c>
       <c r="D39" s="25" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="E39" s="25" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="F39" s="25" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
     </row>
     <row r="40" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="113" t="s">
+      <c r="B40" s="120" t="s">
         <v>157</v>
       </c>
-      <c r="C40" s="113"/>
-      <c r="D40" s="113"/>
+      <c r="C40" s="120"/>
+      <c r="D40" s="120"/>
       <c r="E40" s="34">
         <v>5</v>
       </c>
@@ -4600,13 +4672,13 @@
     </row>
     <row r="41" spans="2:6" ht="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="42" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="107" t="s">
+      <c r="B42" s="112" t="s">
         <v>158</v>
       </c>
-      <c r="C42" s="107"/>
-      <c r="D42" s="107"/>
-      <c r="E42" s="107"/>
-      <c r="F42" s="107"/>
+      <c r="C42" s="112"/>
+      <c r="D42" s="112"/>
+      <c r="E42" s="112"/>
+      <c r="F42" s="112"/>
     </row>
     <row r="43" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B43" s="1" t="s">
@@ -4632,14 +4704,14 @@
       <c r="C44" s="31" t="s">
         <v>164</v>
       </c>
-      <c r="D44" s="142" t="s">
-        <v>586</v>
-      </c>
-      <c r="E44" s="142" t="s">
-        <v>634</v>
-      </c>
-      <c r="F44" s="142" t="s">
-        <v>623</v>
+      <c r="D44" s="110" t="s">
+        <v>578</v>
+      </c>
+      <c r="E44" s="110" t="s">
+        <v>626</v>
+      </c>
+      <c r="F44" s="110" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="45" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -4649,14 +4721,14 @@
       <c r="C45" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="D45" s="142" t="s">
-        <v>578</v>
-      </c>
-      <c r="E45" s="142" t="s">
-        <v>634</v>
-      </c>
-      <c r="F45" s="142" t="s">
-        <v>623</v>
+      <c r="D45" s="110" t="s">
+        <v>570</v>
+      </c>
+      <c r="E45" s="110" t="s">
+        <v>626</v>
+      </c>
+      <c r="F45" s="110" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="46" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -4666,14 +4738,14 @@
       <c r="C46" s="31" t="s">
         <v>168</v>
       </c>
-      <c r="D46" s="142" t="s">
-        <v>582</v>
-      </c>
-      <c r="E46" s="142" t="s">
-        <v>634</v>
-      </c>
-      <c r="F46" s="142" t="s">
-        <v>623</v>
+      <c r="D46" s="110" t="s">
+        <v>574</v>
+      </c>
+      <c r="E46" s="110" t="s">
+        <v>626</v>
+      </c>
+      <c r="F46" s="110" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="47" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -4683,14 +4755,14 @@
       <c r="C47" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="D47" s="142" t="s">
-        <v>616</v>
-      </c>
-      <c r="E47" s="142" t="s">
-        <v>634</v>
-      </c>
-      <c r="F47" s="142" t="s">
-        <v>623</v>
+      <c r="D47" s="110" t="s">
+        <v>608</v>
+      </c>
+      <c r="E47" s="110" t="s">
+        <v>626</v>
+      </c>
+      <c r="F47" s="110" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="48" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -4700,24 +4772,24 @@
       <c r="C48" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="D48" s="142" t="s">
-        <v>582</v>
-      </c>
-      <c r="E48" s="142" t="s">
-        <v>635</v>
-      </c>
-      <c r="F48" s="142" t="s">
-        <v>623</v>
+      <c r="D48" s="110" t="s">
+        <v>574</v>
+      </c>
+      <c r="E48" s="110" t="s">
+        <v>627</v>
+      </c>
+      <c r="F48" s="110" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="49" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="107" t="s">
+      <c r="B49" s="112" t="s">
         <v>173</v>
       </c>
-      <c r="C49" s="107"/>
-      <c r="D49" s="107"/>
-      <c r="E49" s="107"/>
-      <c r="F49" s="107"/>
+      <c r="C49" s="112"/>
+      <c r="D49" s="112"/>
+      <c r="E49" s="112"/>
+      <c r="F49" s="112"/>
     </row>
     <row r="50" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="17" t="s">
@@ -4744,7 +4816,7 @@
         <v>180</v>
       </c>
       <c r="D51" s="25" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E51" s="25"/>
       <c r="F51" s="25"/>
@@ -4757,7 +4829,7 @@
         <v>182</v>
       </c>
       <c r="D52" s="25" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E52" s="25"/>
       <c r="F52" s="25"/>
@@ -4770,7 +4842,7 @@
         <v>184</v>
       </c>
       <c r="D53" s="25" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="E53" s="25"/>
       <c r="F53" s="25"/>
@@ -4783,17 +4855,17 @@
         <v>186</v>
       </c>
       <c r="D54" s="25" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E54" s="25"/>
       <c r="F54" s="25"/>
     </row>
     <row r="55" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="113" t="s">
+      <c r="B55" s="120" t="s">
         <v>187</v>
       </c>
-      <c r="C55" s="113"/>
-      <c r="D55" s="113"/>
+      <c r="C55" s="120"/>
+      <c r="D55" s="120"/>
       <c r="E55" s="34">
         <v>4.5</v>
       </c>
@@ -4809,13 +4881,13 @@
       <c r="F56" s="35"/>
     </row>
     <row r="57" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="112" t="s">
+      <c r="B57" s="121" t="s">
         <v>188</v>
       </c>
-      <c r="C57" s="112"/>
-      <c r="D57" s="112"/>
-      <c r="E57" s="112"/>
-      <c r="F57" s="112"/>
+      <c r="C57" s="121"/>
+      <c r="D57" s="121"/>
+      <c r="E57" s="121"/>
+      <c r="F57" s="121"/>
     </row>
     <row r="58" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="36" t="s">
@@ -4842,11 +4914,11 @@
         <v>191</v>
       </c>
       <c r="D59" s="38" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="E59" s="38"/>
       <c r="F59" s="38" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
     </row>
     <row r="60" spans="2:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -4857,11 +4929,11 @@
         <v>193</v>
       </c>
       <c r="D60" s="40" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E60" s="40"/>
       <c r="F60" s="40" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
     </row>
     <row r="61" spans="2:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -4872,11 +4944,11 @@
         <v>195</v>
       </c>
       <c r="D61" s="38" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E61" s="38"/>
       <c r="F61" s="38" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -4887,11 +4959,11 @@
         <v>197</v>
       </c>
       <c r="D62" s="40" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="E62" s="40"/>
       <c r="F62" s="40" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
     </row>
     <row r="63" spans="2:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -4902,20 +4974,20 @@
         <v>199</v>
       </c>
       <c r="D63" s="38" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E63" s="38"/>
       <c r="F63" s="38" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
     </row>
     <row r="64" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="111" t="s">
+      <c r="B64" s="122" t="s">
         <v>200</v>
       </c>
-      <c r="C64" s="111"/>
-      <c r="D64" s="111"/>
-      <c r="E64" s="141">
+      <c r="C64" s="122"/>
+      <c r="D64" s="122"/>
+      <c r="E64" s="109">
         <v>4.5</v>
       </c>
       <c r="F64" s="42" t="s">
@@ -4930,13 +5002,13 @@
       <c r="F65" s="35"/>
     </row>
     <row r="66" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="112" t="s">
+      <c r="B66" s="121" t="s">
         <v>201</v>
       </c>
-      <c r="C66" s="112"/>
-      <c r="D66" s="112"/>
-      <c r="E66" s="112"/>
-      <c r="F66" s="112"/>
+      <c r="C66" s="121"/>
+      <c r="D66" s="121"/>
+      <c r="E66" s="121"/>
+      <c r="F66" s="121"/>
     </row>
     <row r="67" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B67" s="36" t="s">
@@ -4963,7 +5035,7 @@
         <v>203</v>
       </c>
       <c r="D68" s="38" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E68" s="38"/>
       <c r="F68" s="38"/>
@@ -4976,7 +5048,7 @@
         <v>205</v>
       </c>
       <c r="D69" s="40" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E69" s="40"/>
       <c r="F69" s="40"/>
@@ -4989,7 +5061,7 @@
         <v>207</v>
       </c>
       <c r="D70" s="38" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E70" s="38"/>
       <c r="F70" s="38"/>
@@ -5002,7 +5074,7 @@
         <v>209</v>
       </c>
       <c r="D71" s="40" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E71" s="40"/>
       <c r="F71" s="40"/>
@@ -5015,7 +5087,7 @@
         <v>211</v>
       </c>
       <c r="D72" s="38" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="E72" s="38"/>
       <c r="F72" s="38"/>
@@ -5028,17 +5100,17 @@
         <v>213</v>
       </c>
       <c r="D73" s="40" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="E73" s="40"/>
       <c r="F73" s="40"/>
     </row>
     <row r="74" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="111" t="s">
+      <c r="B74" s="122" t="s">
         <v>214</v>
       </c>
-      <c r="C74" s="111"/>
-      <c r="D74" s="111"/>
+      <c r="C74" s="122"/>
+      <c r="D74" s="122"/>
       <c r="E74" s="41">
         <v>4</v>
       </c>
@@ -5054,13 +5126,13 @@
       <c r="F75" s="35"/>
     </row>
     <row r="76" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="112" t="s">
+      <c r="B76" s="121" t="s">
         <v>215</v>
       </c>
-      <c r="C76" s="112"/>
-      <c r="D76" s="112"/>
-      <c r="E76" s="112"/>
-      <c r="F76" s="112"/>
+      <c r="C76" s="121"/>
+      <c r="D76" s="121"/>
+      <c r="E76" s="121"/>
+      <c r="F76" s="121"/>
     </row>
     <row r="77" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B77" s="36" t="s">
@@ -5087,7 +5159,7 @@
         <v>217</v>
       </c>
       <c r="D78" s="38" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="E78" s="38"/>
       <c r="F78" s="38"/>
@@ -5100,7 +5172,7 @@
         <v>219</v>
       </c>
       <c r="D79" s="40" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E79" s="40"/>
       <c r="F79" s="40"/>
@@ -5113,7 +5185,7 @@
         <v>221</v>
       </c>
       <c r="D80" s="38" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="E80" s="38"/>
       <c r="F80" s="38"/>
@@ -5126,7 +5198,7 @@
         <v>223</v>
       </c>
       <c r="D81" s="40" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="E81" s="40"/>
       <c r="F81" s="40"/>
@@ -5139,17 +5211,17 @@
         <v>225</v>
       </c>
       <c r="D82" s="38" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E82" s="38"/>
       <c r="F82" s="38"/>
     </row>
     <row r="83" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="111" t="s">
+      <c r="B83" s="122" t="s">
         <v>226</v>
       </c>
-      <c r="C83" s="111"/>
-      <c r="D83" s="111"/>
+      <c r="C83" s="122"/>
+      <c r="D83" s="122"/>
       <c r="E83" s="41">
         <v>4</v>
       </c>
@@ -5165,13 +5237,13 @@
       <c r="F84" s="35"/>
     </row>
     <row r="85" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="112" t="s">
+      <c r="B85" s="121" t="s">
         <v>227</v>
       </c>
-      <c r="C85" s="112"/>
-      <c r="D85" s="112"/>
-      <c r="E85" s="112"/>
-      <c r="F85" s="112"/>
+      <c r="C85" s="121"/>
+      <c r="D85" s="121"/>
+      <c r="E85" s="121"/>
+      <c r="F85" s="121"/>
     </row>
     <row r="86" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="36" t="s">
@@ -5198,7 +5270,7 @@
         <v>229</v>
       </c>
       <c r="D87" s="38" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="E87" s="38"/>
       <c r="F87" s="38"/>
@@ -5211,7 +5283,7 @@
         <v>231</v>
       </c>
       <c r="D88" s="40" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="E88" s="40"/>
       <c r="F88" s="40"/>
@@ -5224,7 +5296,7 @@
         <v>233</v>
       </c>
       <c r="D89" s="38" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="E89" s="38"/>
       <c r="F89" s="38"/>
@@ -5237,17 +5309,17 @@
         <v>235</v>
       </c>
       <c r="D90" s="40" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="E90" s="40"/>
       <c r="F90" s="40"/>
     </row>
     <row r="91" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B91" s="111" t="s">
+      <c r="B91" s="122" t="s">
         <v>236</v>
       </c>
-      <c r="C91" s="111"/>
-      <c r="D91" s="111"/>
+      <c r="C91" s="122"/>
+      <c r="D91" s="122"/>
       <c r="E91" s="41">
         <v>5</v>
       </c>
@@ -5257,32 +5329,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B64:D64"/>
     <mergeCell ref="B91:D91"/>
     <mergeCell ref="B66:F66"/>
     <mergeCell ref="B74:D74"/>
     <mergeCell ref="B76:F76"/>
     <mergeCell ref="B83:D83"/>
     <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -5302,108 +5374,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="115" t="s">
+      <c r="B1" s="116" t="s">
         <v>237</v>
       </c>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
     </row>
     <row r="2" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="117" t="s">
         <v>92</v>
       </c>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
     </row>
     <row r="3" spans="2:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="107" t="s">
+      <c r="B4" s="112" t="s">
         <v>238</v>
       </c>
-      <c r="C4" s="107"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
     </row>
     <row r="5" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="114" t="s">
+      <c r="C5" s="118" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="114"/>
-      <c r="E5" s="114"/>
-      <c r="F5" s="114"/>
+      <c r="D5" s="118"/>
+      <c r="E5" s="118"/>
+      <c r="F5" s="118"/>
     </row>
     <row r="6" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="114">
+      <c r="C6" s="118">
         <v>26</v>
       </c>
-      <c r="D6" s="114"/>
-      <c r="E6" s="114"/>
-      <c r="F6" s="114"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="118"/>
     </row>
     <row r="7" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="114" t="s">
-        <v>561</v>
-      </c>
-      <c r="D7" s="114"/>
-      <c r="E7" s="114"/>
-      <c r="F7" s="114"/>
+      <c r="C7" s="118" t="s">
+        <v>553</v>
+      </c>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
     </row>
     <row r="8" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="114" t="s">
-        <v>560</v>
-      </c>
-      <c r="D8" s="114"/>
-      <c r="E8" s="114"/>
-      <c r="F8" s="114"/>
+      <c r="C8" s="118" t="s">
+        <v>552</v>
+      </c>
+      <c r="D8" s="118"/>
+      <c r="E8" s="118"/>
+      <c r="F8" s="118"/>
     </row>
     <row r="9" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C9" s="114" t="s">
-        <v>570</v>
-      </c>
-      <c r="D9" s="114"/>
-      <c r="E9" s="114"/>
-      <c r="F9" s="114"/>
+      <c r="C9" s="118" t="s">
+        <v>562</v>
+      </c>
+      <c r="D9" s="118"/>
+      <c r="E9" s="118"/>
+      <c r="F9" s="118"/>
     </row>
     <row r="10" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C10" s="138">
+      <c r="C10" s="119">
         <v>0.63750000000000007</v>
       </c>
-      <c r="D10" s="114"/>
-      <c r="E10" s="114"/>
-      <c r="F10" s="114"/>
+      <c r="D10" s="118"/>
+      <c r="E10" s="118"/>
+      <c r="F10" s="118"/>
     </row>
     <row r="11" spans="2:6" ht="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="107" t="s">
+      <c r="B12" s="112" t="s">
         <v>239</v>
       </c>
-      <c r="C12" s="107"/>
-      <c r="D12" s="107"/>
-      <c r="E12" s="107"/>
-      <c r="F12" s="107"/>
+      <c r="C12" s="112"/>
+      <c r="D12" s="112"/>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
     </row>
     <row r="13" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="1" t="s">
@@ -5430,10 +5502,10 @@
         <v>103</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="F14" s="32"/>
     </row>
@@ -5445,10 +5517,10 @@
         <v>105</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="F15" s="32"/>
     </row>
@@ -5460,10 +5532,10 @@
         <v>107</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="F16" s="32"/>
     </row>
@@ -5475,10 +5547,10 @@
         <v>109</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="E17" s="32" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="F17" s="32"/>
     </row>
@@ -5490,19 +5562,19 @@
         <v>111</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="F18" s="32"/>
     </row>
     <row r="19" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="113" t="s">
+      <c r="B19" s="120" t="s">
         <v>112</v>
       </c>
-      <c r="C19" s="113"/>
-      <c r="D19" s="113"/>
+      <c r="C19" s="120"/>
+      <c r="D19" s="120"/>
       <c r="E19" s="34">
         <v>5</v>
       </c>
@@ -5512,13 +5584,13 @@
     </row>
     <row r="20" spans="2:6" ht="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="21" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="107" t="s">
+      <c r="B21" s="112" t="s">
         <v>240</v>
       </c>
-      <c r="C21" s="107"/>
-      <c r="D21" s="107"/>
-      <c r="E21" s="107"/>
-      <c r="F21" s="107"/>
+      <c r="C21" s="112"/>
+      <c r="D21" s="112"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
     </row>
     <row r="22" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="1" t="s">
@@ -5545,13 +5617,13 @@
         <v>120</v>
       </c>
       <c r="D23" s="25" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="E23" s="31" t="s">
         <v>121</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
     </row>
     <row r="24" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -5562,13 +5634,13 @@
         <v>123</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="E24" s="19" t="s">
         <v>124</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
     </row>
     <row r="25" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -5579,13 +5651,13 @@
         <v>126</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="E25" s="31" t="s">
         <v>127</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
     </row>
     <row r="26" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -5595,14 +5667,14 @@
       <c r="C26" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="D26" s="140">
+      <c r="D26" s="108">
         <v>0.01</v>
       </c>
       <c r="E26" s="19" t="s">
         <v>130</v>
       </c>
       <c r="F26" s="25" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
     </row>
     <row r="27" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -5613,13 +5685,13 @@
         <v>132</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="E27" s="31" t="s">
         <v>133</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
     </row>
     <row r="28" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -5630,21 +5702,21 @@
         <v>135</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="E28" s="19" t="s">
         <v>136</v>
       </c>
       <c r="F28" s="25" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
     </row>
     <row r="29" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="113" t="s">
+      <c r="B29" s="120" t="s">
         <v>137</v>
       </c>
-      <c r="C29" s="113"/>
-      <c r="D29" s="113"/>
+      <c r="C29" s="120"/>
+      <c r="D29" s="120"/>
       <c r="E29" s="34">
         <v>5</v>
       </c>
@@ -5654,13 +5726,13 @@
     </row>
     <row r="30" spans="2:6" ht="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="31" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="107" t="s">
+      <c r="B31" s="112" t="s">
         <v>241</v>
       </c>
-      <c r="C31" s="107"/>
-      <c r="D31" s="107"/>
-      <c r="E31" s="107"/>
-      <c r="F31" s="107"/>
+      <c r="C31" s="112"/>
+      <c r="D31" s="112"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
     </row>
     <row r="32" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="1" t="s">
@@ -5690,7 +5762,7 @@
         <v>10</v>
       </c>
       <c r="E33" s="25" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="F33" s="25"/>
     </row>
@@ -5702,10 +5774,10 @@
         <v>146</v>
       </c>
       <c r="D34" s="25" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="E34" s="25" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="F34" s="25"/>
     </row>
@@ -5717,10 +5789,10 @@
         <v>148</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E35" s="25" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="F35" s="25"/>
     </row>
@@ -5732,7 +5804,7 @@
         <v>150</v>
       </c>
       <c r="D36" s="25" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E36" s="25"/>
       <c r="F36" s="25"/>
@@ -5745,7 +5817,7 @@
         <v>152</v>
       </c>
       <c r="D37" s="25" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E37" s="25"/>
       <c r="F37" s="25"/>
@@ -5758,7 +5830,7 @@
         <v>154</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E38" s="25"/>
       <c r="F38" s="25"/>
@@ -5771,17 +5843,17 @@
         <v>156</v>
       </c>
       <c r="D39" s="25" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="E39" s="25"/>
       <c r="F39" s="25"/>
     </row>
     <row r="40" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="113" t="s">
+      <c r="B40" s="120" t="s">
         <v>157</v>
       </c>
-      <c r="C40" s="113"/>
-      <c r="D40" s="113"/>
+      <c r="C40" s="120"/>
+      <c r="D40" s="120"/>
       <c r="E40" s="34">
         <v>3.5</v>
       </c>
@@ -5791,13 +5863,13 @@
     </row>
     <row r="41" spans="2:6" ht="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="42" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="107" t="s">
+      <c r="B42" s="112" t="s">
         <v>242</v>
       </c>
-      <c r="C42" s="107"/>
-      <c r="D42" s="107"/>
-      <c r="E42" s="107"/>
-      <c r="F42" s="107"/>
+      <c r="C42" s="112"/>
+      <c r="D42" s="112"/>
+      <c r="E42" s="112"/>
+      <c r="F42" s="112"/>
     </row>
     <row r="43" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B43" s="1" t="s">
@@ -5824,13 +5896,13 @@
         <v>164</v>
       </c>
       <c r="D44" s="25" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="E44" s="25" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="F44" s="25" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="45" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -5841,13 +5913,13 @@
         <v>166</v>
       </c>
       <c r="D45" s="25" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="E45" s="25" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="F45" s="25" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="46" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -5858,13 +5930,13 @@
         <v>168</v>
       </c>
       <c r="D46" s="25" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="E46" s="25" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="F46" s="25" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
     </row>
     <row r="47" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -5875,13 +5947,13 @@
         <v>170</v>
       </c>
       <c r="D47" s="25" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="E47" s="25" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="F47" s="25" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
     </row>
     <row r="48" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
@@ -5892,23 +5964,23 @@
         <v>172</v>
       </c>
       <c r="D48" s="25" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="E48" s="25" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="F48" s="25" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
     </row>
     <row r="49" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="107" t="s">
+      <c r="B49" s="112" t="s">
         <v>173</v>
       </c>
-      <c r="C49" s="107"/>
-      <c r="D49" s="107"/>
-      <c r="E49" s="107"/>
-      <c r="F49" s="107"/>
+      <c r="C49" s="112"/>
+      <c r="D49" s="112"/>
+      <c r="E49" s="112"/>
+      <c r="F49" s="112"/>
     </row>
     <row r="50" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="17" t="s">
@@ -5935,7 +6007,7 @@
         <v>180</v>
       </c>
       <c r="D51" s="25" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="E51" s="25"/>
       <c r="F51" s="25"/>
@@ -5948,7 +6020,7 @@
         <v>182</v>
       </c>
       <c r="D52" s="25" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="E52" s="25"/>
       <c r="F52" s="25"/>
@@ -5961,7 +6033,7 @@
         <v>184</v>
       </c>
       <c r="D53" s="25" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="E53" s="25"/>
       <c r="F53" s="25"/>
@@ -5974,17 +6046,17 @@
         <v>186</v>
       </c>
       <c r="D54" s="25" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="E54" s="25"/>
       <c r="F54" s="25"/>
     </row>
     <row r="55" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="113" t="s">
+      <c r="B55" s="120" t="s">
         <v>187</v>
       </c>
-      <c r="C55" s="113"/>
-      <c r="D55" s="113"/>
+      <c r="C55" s="120"/>
+      <c r="D55" s="120"/>
       <c r="E55" s="34">
         <v>4</v>
       </c>
@@ -6000,13 +6072,13 @@
       <c r="F56" s="35"/>
     </row>
     <row r="57" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="112" t="s">
+      <c r="B57" s="121" t="s">
         <v>243</v>
       </c>
-      <c r="C57" s="112"/>
-      <c r="D57" s="112"/>
-      <c r="E57" s="112"/>
-      <c r="F57" s="112"/>
+      <c r="C57" s="121"/>
+      <c r="D57" s="121"/>
+      <c r="E57" s="121"/>
+      <c r="F57" s="121"/>
     </row>
     <row r="58" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="36" t="s">
@@ -6033,7 +6105,7 @@
         <v>191</v>
       </c>
       <c r="D59" s="38" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="E59" s="38"/>
       <c r="F59" s="38"/>
@@ -6046,7 +6118,7 @@
         <v>193</v>
       </c>
       <c r="D60" s="40" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E60" s="40"/>
       <c r="F60" s="40"/>
@@ -6059,7 +6131,7 @@
         <v>195</v>
       </c>
       <c r="D61" s="38" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E61" s="38"/>
       <c r="F61" s="38"/>
@@ -6072,7 +6144,7 @@
         <v>197</v>
       </c>
       <c r="D62" s="40" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E62" s="40"/>
       <c r="F62" s="40"/>
@@ -6085,17 +6157,17 @@
         <v>199</v>
       </c>
       <c r="D63" s="38" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E63" s="38"/>
       <c r="F63" s="38"/>
     </row>
     <row r="64" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="111" t="s">
+      <c r="B64" s="122" t="s">
         <v>200</v>
       </c>
-      <c r="C64" s="111"/>
-      <c r="D64" s="111"/>
+      <c r="C64" s="122"/>
+      <c r="D64" s="122"/>
       <c r="E64" s="41">
         <v>5</v>
       </c>
@@ -6111,13 +6183,13 @@
       <c r="F65" s="35"/>
     </row>
     <row r="66" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="112" t="s">
+      <c r="B66" s="121" t="s">
         <v>244</v>
       </c>
-      <c r="C66" s="112"/>
-      <c r="D66" s="112"/>
-      <c r="E66" s="112"/>
-      <c r="F66" s="112"/>
+      <c r="C66" s="121"/>
+      <c r="D66" s="121"/>
+      <c r="E66" s="121"/>
+      <c r="F66" s="121"/>
     </row>
     <row r="67" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B67" s="36" t="s">
@@ -6144,7 +6216,7 @@
         <v>203</v>
       </c>
       <c r="D68" s="38" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="E68" s="38"/>
       <c r="F68" s="38"/>
@@ -6157,7 +6229,7 @@
         <v>205</v>
       </c>
       <c r="D69" s="40" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="E69" s="40"/>
       <c r="F69" s="40"/>
@@ -6170,7 +6242,7 @@
         <v>207</v>
       </c>
       <c r="D70" s="38" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="E70" s="38"/>
       <c r="F70" s="38"/>
@@ -6183,7 +6255,7 @@
         <v>209</v>
       </c>
       <c r="D71" s="40" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="E71" s="40"/>
       <c r="F71" s="40"/>
@@ -6196,7 +6268,7 @@
         <v>211</v>
       </c>
       <c r="D72" s="38" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="E72" s="38"/>
       <c r="F72" s="38"/>
@@ -6209,17 +6281,17 @@
         <v>213</v>
       </c>
       <c r="D73" s="40" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="E73" s="40"/>
       <c r="F73" s="40"/>
     </row>
     <row r="74" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="111" t="s">
+      <c r="B74" s="122" t="s">
         <v>214</v>
       </c>
-      <c r="C74" s="111"/>
-      <c r="D74" s="111"/>
+      <c r="C74" s="122"/>
+      <c r="D74" s="122"/>
       <c r="E74" s="41">
         <v>5</v>
       </c>
@@ -6235,13 +6307,13 @@
       <c r="F75" s="35"/>
     </row>
     <row r="76" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="112" t="s">
+      <c r="B76" s="121" t="s">
         <v>245</v>
       </c>
-      <c r="C76" s="112"/>
-      <c r="D76" s="112"/>
-      <c r="E76" s="112"/>
-      <c r="F76" s="112"/>
+      <c r="C76" s="121"/>
+      <c r="D76" s="121"/>
+      <c r="E76" s="121"/>
+      <c r="F76" s="121"/>
     </row>
     <row r="77" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B77" s="36" t="s">
@@ -6268,7 +6340,7 @@
         <v>217</v>
       </c>
       <c r="D78" s="38" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="E78" s="38"/>
       <c r="F78" s="38"/>
@@ -6281,7 +6353,7 @@
         <v>219</v>
       </c>
       <c r="D79" s="40" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="E79" s="40"/>
       <c r="F79" s="40"/>
@@ -6294,7 +6366,7 @@
         <v>221</v>
       </c>
       <c r="D80" s="38" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="E80" s="38"/>
       <c r="F80" s="38"/>
@@ -6307,7 +6379,7 @@
         <v>223</v>
       </c>
       <c r="D81" s="40" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="E81" s="40"/>
       <c r="F81" s="40"/>
@@ -6320,17 +6392,17 @@
         <v>225</v>
       </c>
       <c r="D82" s="38" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="E82" s="38"/>
       <c r="F82" s="38"/>
     </row>
     <row r="83" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="111" t="s">
+      <c r="B83" s="122" t="s">
         <v>226</v>
       </c>
-      <c r="C83" s="111"/>
-      <c r="D83" s="111"/>
+      <c r="C83" s="122"/>
+      <c r="D83" s="122"/>
       <c r="E83" s="41">
         <v>3</v>
       </c>
@@ -6346,13 +6418,13 @@
       <c r="F84" s="35"/>
     </row>
     <row r="85" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="112" t="s">
+      <c r="B85" s="121" t="s">
         <v>246</v>
       </c>
-      <c r="C85" s="112"/>
-      <c r="D85" s="112"/>
-      <c r="E85" s="112"/>
-      <c r="F85" s="112"/>
+      <c r="C85" s="121"/>
+      <c r="D85" s="121"/>
+      <c r="E85" s="121"/>
+      <c r="F85" s="121"/>
     </row>
     <row r="86" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="36" t="s">
@@ -6379,7 +6451,7 @@
         <v>229</v>
       </c>
       <c r="D87" s="38" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="E87" s="38"/>
       <c r="F87" s="38"/>
@@ -6392,7 +6464,7 @@
         <v>231</v>
       </c>
       <c r="D88" s="40" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E88" s="40"/>
       <c r="F88" s="40"/>
@@ -6405,7 +6477,7 @@
         <v>233</v>
       </c>
       <c r="D89" s="38" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E89" s="38"/>
       <c r="F89" s="38"/>
@@ -6418,17 +6490,17 @@
         <v>235</v>
       </c>
       <c r="D90" s="40" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="E90" s="40"/>
       <c r="F90" s="40"/>
     </row>
     <row r="91" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B91" s="111" t="s">
+      <c r="B91" s="122" t="s">
         <v>236</v>
       </c>
-      <c r="C91" s="111"/>
-      <c r="D91" s="111"/>
+      <c r="C91" s="122"/>
+      <c r="D91" s="122"/>
       <c r="E91" s="41">
         <v>4</v>
       </c>
@@ -6438,32 +6510,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B64:D64"/>
     <mergeCell ref="B91:D91"/>
     <mergeCell ref="B66:F66"/>
     <mergeCell ref="B74:D74"/>
     <mergeCell ref="B76:F76"/>
     <mergeCell ref="B83:D83"/>
     <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6484,97 +6556,97 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="115" t="s">
+      <c r="B1" s="116" t="s">
         <v>247</v>
       </c>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
     </row>
     <row r="2" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="117" t="s">
         <v>248</v>
       </c>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
     </row>
     <row r="3" spans="2:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="107" t="s">
+      <c r="B4" s="112" t="s">
         <v>249</v>
       </c>
-      <c r="C4" s="107"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
     </row>
     <row r="5" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="143" t="s">
-        <v>636</v>
-      </c>
-      <c r="D5" s="114"/>
-      <c r="E5" s="114"/>
-      <c r="F5" s="114"/>
+      <c r="C5" s="123" t="s">
+        <v>628</v>
+      </c>
+      <c r="D5" s="118"/>
+      <c r="E5" s="118"/>
+      <c r="F5" s="118"/>
     </row>
     <row r="6" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="C6" s="143" t="s">
-        <v>565</v>
-      </c>
-      <c r="D6" s="114"/>
-      <c r="E6" s="114"/>
-      <c r="F6" s="114"/>
+      <c r="C6" s="123" t="s">
+        <v>557</v>
+      </c>
+      <c r="D6" s="118"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="118"/>
     </row>
     <row r="7" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C7" s="143" t="s">
-        <v>566</v>
-      </c>
-      <c r="D7" s="114"/>
-      <c r="E7" s="114"/>
-      <c r="F7" s="114"/>
+      <c r="C7" s="123" t="s">
+        <v>558</v>
+      </c>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
     </row>
     <row r="8" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="143" t="s">
-        <v>569</v>
-      </c>
-      <c r="D8" s="114"/>
-      <c r="E8" s="114"/>
-      <c r="F8" s="114"/>
+      <c r="C8" s="123" t="s">
+        <v>561</v>
+      </c>
+      <c r="D8" s="118"/>
+      <c r="E8" s="118"/>
+      <c r="F8" s="118"/>
     </row>
     <row r="9" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="C9" s="143" t="s">
-        <v>570</v>
-      </c>
-      <c r="D9" s="114"/>
-      <c r="E9" s="114"/>
-      <c r="F9" s="114"/>
+      <c r="C9" s="123" t="s">
+        <v>562</v>
+      </c>
+      <c r="D9" s="118"/>
+      <c r="E9" s="118"/>
+      <c r="F9" s="118"/>
     </row>
     <row r="10" spans="2:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="11" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="107" t="s">
+      <c r="B11" s="112" t="s">
         <v>253</v>
       </c>
-      <c r="C11" s="107"/>
-      <c r="D11" s="107"/>
-      <c r="E11" s="107"/>
-      <c r="F11" s="107"/>
+      <c r="C11" s="112"/>
+      <c r="D11" s="112"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
     </row>
     <row r="12" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="18" t="s">
@@ -6604,7 +6676,7 @@
         <v>260</v>
       </c>
       <c r="E13" s="46" t="s">
-        <v>261</v>
+        <v>641</v>
       </c>
       <c r="F13" s="47">
         <f>C13*0.15</f>
@@ -6613,16 +6685,16 @@
     </row>
     <row r="14" spans="2:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="48" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C14" s="44">
         <v>4</v>
       </c>
       <c r="D14" s="49" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E14" s="46" t="s">
-        <v>264</v>
+        <v>642</v>
       </c>
       <c r="F14" s="50">
         <f>C14*0.12</f>
@@ -6631,16 +6703,16 @@
     </row>
     <row r="15" spans="2:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="43" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C15" s="44">
         <v>5</v>
       </c>
       <c r="D15" s="45" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E15" s="46" t="s">
-        <v>267</v>
+        <v>643</v>
       </c>
       <c r="F15" s="47">
         <f>C15*0.1</f>
@@ -6649,7 +6721,7 @@
     </row>
     <row r="16" spans="2:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="48" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C16" s="44">
         <v>4.5</v>
@@ -6658,7 +6730,7 @@
         <v>260</v>
       </c>
       <c r="E16" s="46" t="s">
-        <v>269</v>
+        <v>644</v>
       </c>
       <c r="F16" s="50">
         <f>C16*0.15</f>
@@ -6667,7 +6739,7 @@
     </row>
     <row r="17" spans="2:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="43" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C17" s="44">
         <v>4.5</v>
@@ -6676,7 +6748,7 @@
         <v>260</v>
       </c>
       <c r="E17" s="46" t="s">
-        <v>271</v>
+        <v>645</v>
       </c>
       <c r="F17" s="47">
         <f>C17*0.15</f>
@@ -6685,7 +6757,7 @@
     </row>
     <row r="18" spans="2:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="48" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C18" s="44">
         <v>4</v>
@@ -6694,7 +6766,7 @@
         <v>260</v>
       </c>
       <c r="E18" s="46" t="s">
-        <v>273</v>
+        <v>646</v>
       </c>
       <c r="F18" s="50">
         <f>C18*0.15</f>
@@ -6703,16 +6775,16 @@
     </row>
     <row r="19" spans="2:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="43" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C19" s="44">
         <v>4</v>
       </c>
       <c r="D19" s="45" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="E19" s="46" t="s">
-        <v>276</v>
+        <v>647</v>
       </c>
       <c r="F19" s="47">
         <f>C19*0.08</f>
@@ -6721,16 +6793,16 @@
     </row>
     <row r="20" spans="2:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="48" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="C20" s="44">
         <v>5</v>
       </c>
       <c r="D20" s="49" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E20" s="46" t="s">
-        <v>278</v>
+        <v>648</v>
       </c>
       <c r="F20" s="50">
         <f>C20*0.1</f>
@@ -6738,12 +6810,12 @@
       </c>
     </row>
     <row r="21" spans="2:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="120" t="s">
-        <v>279</v>
-      </c>
-      <c r="C21" s="120"/>
-      <c r="D21" s="120"/>
-      <c r="E21" s="120"/>
+      <c r="B21" s="124" t="s">
+        <v>271</v>
+      </c>
+      <c r="C21" s="124"/>
+      <c r="D21" s="124"/>
+      <c r="E21" s="124"/>
       <c r="F21" s="51">
         <f>SUM(F13:F20)</f>
         <v>4.4249999999999989</v>
@@ -6751,102 +6823,92 @@
     </row>
     <row r="22" spans="2:6" ht="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="23" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="107" t="s">
-        <v>280</v>
-      </c>
-      <c r="C23" s="107"/>
-      <c r="D23" s="107"/>
-      <c r="E23" s="107"/>
-      <c r="F23" s="107"/>
+      <c r="B23" s="112" t="s">
+        <v>272</v>
+      </c>
+      <c r="C23" s="112"/>
+      <c r="D23" s="112"/>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
     </row>
     <row r="24" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="17" t="s">
         <v>189</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>281</v>
-      </c>
-      <c r="D24" s="119"/>
-      <c r="E24" s="119"/>
+        <v>273</v>
+      </c>
+      <c r="D24" s="127"/>
+      <c r="E24" s="127"/>
       <c r="F24" s="17"/>
     </row>
     <row r="25" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="52" t="s">
-        <v>282</v>
-      </c>
-      <c r="C25" s="118" t="s">
-        <v>283</v>
-      </c>
-      <c r="D25" s="118"/>
+        <v>274</v>
+      </c>
+      <c r="C25" s="126" t="s">
+        <v>275</v>
+      </c>
+      <c r="D25" s="126"/>
       <c r="E25" s="53"/>
       <c r="F25" s="54" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
     </row>
     <row r="26" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="55" t="s">
-        <v>285</v>
-      </c>
-      <c r="C26" s="117" t="s">
-        <v>286</v>
-      </c>
-      <c r="D26" s="117"/>
+        <v>277</v>
+      </c>
+      <c r="C26" s="125" t="s">
+        <v>278</v>
+      </c>
+      <c r="D26" s="125"/>
       <c r="E26" s="53"/>
       <c r="F26" s="54" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
     </row>
     <row r="27" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="52" t="s">
-        <v>288</v>
-      </c>
-      <c r="C27" s="118" t="s">
-        <v>289</v>
-      </c>
-      <c r="D27" s="118"/>
+        <v>280</v>
+      </c>
+      <c r="C27" s="126" t="s">
+        <v>281</v>
+      </c>
+      <c r="D27" s="126"/>
       <c r="E27" s="53"/>
       <c r="F27" s="54" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
     </row>
     <row r="28" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="55" t="s">
-        <v>291</v>
-      </c>
-      <c r="C28" s="117" t="s">
-        <v>292</v>
-      </c>
-      <c r="D28" s="117"/>
+        <v>283</v>
+      </c>
+      <c r="C28" s="125" t="s">
+        <v>284</v>
+      </c>
+      <c r="D28" s="125"/>
       <c r="E28" s="53"/>
       <c r="F28" s="54" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
     </row>
     <row r="29" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="52" t="s">
-        <v>294</v>
-      </c>
-      <c r="C29" s="118" t="s">
-        <v>295</v>
-      </c>
-      <c r="D29" s="118"/>
+        <v>286</v>
+      </c>
+      <c r="C29" s="126" t="s">
+        <v>287</v>
+      </c>
+      <c r="D29" s="126"/>
       <c r="E29" s="53"/>
       <c r="F29" s="54" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B21:E21"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="B23:F23"/>
@@ -6854,6 +6916,16 @@
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6874,97 +6946,97 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="115" t="s">
-        <v>297</v>
-      </c>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
+      <c r="B1" s="116" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
     </row>
     <row r="2" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="128" t="s">
         <v>248</v>
       </c>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
     </row>
     <row r="3" spans="2:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="107" t="s">
+      <c r="B4" s="112" t="s">
         <v>249</v>
       </c>
-      <c r="C4" s="107"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
     </row>
     <row r="5" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="114" t="s">
+      <c r="C5" s="118" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="114"/>
-      <c r="E5" s="114"/>
-      <c r="F5" s="114"/>
+      <c r="D5" s="118"/>
+      <c r="E5" s="118"/>
+      <c r="F5" s="118"/>
     </row>
     <row r="6" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="C6" s="114">
+      <c r="C6" s="118">
         <v>26</v>
       </c>
-      <c r="D6" s="114"/>
-      <c r="E6" s="114"/>
-      <c r="F6" s="114"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="118"/>
     </row>
     <row r="7" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C7" s="114" t="s">
-        <v>561</v>
-      </c>
-      <c r="D7" s="114"/>
-      <c r="E7" s="114"/>
-      <c r="F7" s="114"/>
+      <c r="C7" s="118" t="s">
+        <v>553</v>
+      </c>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
     </row>
     <row r="8" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="114" t="s">
-        <v>560</v>
-      </c>
-      <c r="D8" s="114"/>
-      <c r="E8" s="114"/>
-      <c r="F8" s="114"/>
+      <c r="C8" s="118" t="s">
+        <v>552</v>
+      </c>
+      <c r="D8" s="118"/>
+      <c r="E8" s="118"/>
+      <c r="F8" s="118"/>
     </row>
     <row r="9" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="C9" s="114" t="s">
-        <v>570</v>
-      </c>
-      <c r="D9" s="114"/>
-      <c r="E9" s="114"/>
-      <c r="F9" s="114"/>
+      <c r="C9" s="118" t="s">
+        <v>562</v>
+      </c>
+      <c r="D9" s="118"/>
+      <c r="E9" s="118"/>
+      <c r="F9" s="118"/>
     </row>
     <row r="10" spans="2:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="11" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="107" t="s">
+      <c r="B11" s="112" t="s">
         <v>253</v>
       </c>
-      <c r="C11" s="107"/>
-      <c r="D11" s="107"/>
-      <c r="E11" s="107"/>
-      <c r="F11" s="107"/>
+      <c r="C11" s="112"/>
+      <c r="D11" s="112"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
     </row>
     <row r="12" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="18" t="s">
@@ -6994,7 +7066,7 @@
         <v>260</v>
       </c>
       <c r="E13" s="46" t="s">
-        <v>261</v>
+        <v>649</v>
       </c>
       <c r="F13" s="47">
         <f>C13*0.15</f>
@@ -7003,16 +7075,16 @@
     </row>
     <row r="14" spans="2:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="48" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C14" s="44">
         <v>5</v>
       </c>
       <c r="D14" s="49" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E14" s="46" t="s">
-        <v>264</v>
+        <v>650</v>
       </c>
       <c r="F14" s="50">
         <f>C14*0.12</f>
@@ -7021,16 +7093,16 @@
     </row>
     <row r="15" spans="2:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="43" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C15" s="44">
         <v>3.5</v>
       </c>
       <c r="D15" s="45" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E15" s="46" t="s">
-        <v>267</v>
+        <v>651</v>
       </c>
       <c r="F15" s="47">
         <f>C15*0.1</f>
@@ -7039,7 +7111,7 @@
     </row>
     <row r="16" spans="2:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="48" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C16" s="44">
         <v>4</v>
@@ -7048,7 +7120,7 @@
         <v>260</v>
       </c>
       <c r="E16" s="46" t="s">
-        <v>269</v>
+        <v>652</v>
       </c>
       <c r="F16" s="50">
         <f>C16*0.15</f>
@@ -7057,7 +7129,7 @@
     </row>
     <row r="17" spans="2:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="43" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C17" s="44">
         <v>5</v>
@@ -7066,7 +7138,7 @@
         <v>260</v>
       </c>
       <c r="E17" s="46" t="s">
-        <v>271</v>
+        <v>653</v>
       </c>
       <c r="F17" s="47">
         <f>C17*0.15</f>
@@ -7075,7 +7147,7 @@
     </row>
     <row r="18" spans="2:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="48" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C18" s="44">
         <v>5</v>
@@ -7084,7 +7156,7 @@
         <v>260</v>
       </c>
       <c r="E18" s="46" t="s">
-        <v>273</v>
+        <v>654</v>
       </c>
       <c r="F18" s="50">
         <f>C18*0.15</f>
@@ -7093,16 +7165,16 @@
     </row>
     <row r="19" spans="2:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="43" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C19" s="44">
         <v>3</v>
       </c>
       <c r="D19" s="45" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="E19" s="46" t="s">
-        <v>276</v>
+        <v>655</v>
       </c>
       <c r="F19" s="47">
         <f>C19*0.08</f>
@@ -7111,16 +7183,16 @@
     </row>
     <row r="20" spans="2:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="48" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="C20" s="44">
         <v>4</v>
       </c>
       <c r="D20" s="49" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E20" s="46" t="s">
-        <v>278</v>
+        <v>656</v>
       </c>
       <c r="F20" s="50">
         <f>C20*0.1</f>
@@ -7128,12 +7200,12 @@
       </c>
     </row>
     <row r="21" spans="2:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="120" t="s">
-        <v>279</v>
-      </c>
-      <c r="C21" s="120"/>
-      <c r="D21" s="120"/>
-      <c r="E21" s="120"/>
+      <c r="B21" s="124" t="s">
+        <v>271</v>
+      </c>
+      <c r="C21" s="124"/>
+      <c r="D21" s="124"/>
+      <c r="E21" s="124"/>
       <c r="F21" s="51">
         <f>SUM(F13:F20)</f>
         <v>4.4400000000000004</v>
@@ -7141,102 +7213,92 @@
     </row>
     <row r="22" spans="2:6" ht="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="23" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="107" t="s">
-        <v>280</v>
-      </c>
-      <c r="C23" s="107"/>
-      <c r="D23" s="107"/>
-      <c r="E23" s="107"/>
-      <c r="F23" s="107"/>
+      <c r="B23" s="112" t="s">
+        <v>272</v>
+      </c>
+      <c r="C23" s="112"/>
+      <c r="D23" s="112"/>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
     </row>
     <row r="24" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="17" t="s">
         <v>189</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>281</v>
-      </c>
-      <c r="D24" s="119"/>
-      <c r="E24" s="119"/>
+        <v>273</v>
+      </c>
+      <c r="D24" s="127"/>
+      <c r="E24" s="127"/>
       <c r="F24" s="17"/>
     </row>
     <row r="25" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="52" t="s">
-        <v>282</v>
-      </c>
-      <c r="C25" s="118" t="s">
-        <v>283</v>
-      </c>
-      <c r="D25" s="118"/>
+        <v>274</v>
+      </c>
+      <c r="C25" s="126" t="s">
+        <v>275</v>
+      </c>
+      <c r="D25" s="126"/>
       <c r="E25" s="53"/>
       <c r="F25" s="54" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
     </row>
     <row r="26" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="55" t="s">
-        <v>285</v>
-      </c>
-      <c r="C26" s="117" t="s">
-        <v>286</v>
-      </c>
-      <c r="D26" s="117"/>
+        <v>277</v>
+      </c>
+      <c r="C26" s="125" t="s">
+        <v>278</v>
+      </c>
+      <c r="D26" s="125"/>
       <c r="E26" s="53"/>
       <c r="F26" s="54" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
     </row>
     <row r="27" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="52" t="s">
-        <v>288</v>
-      </c>
-      <c r="C27" s="118" t="s">
-        <v>289</v>
-      </c>
-      <c r="D27" s="118"/>
+        <v>280</v>
+      </c>
+      <c r="C27" s="126" t="s">
+        <v>281</v>
+      </c>
+      <c r="D27" s="126"/>
       <c r="E27" s="53"/>
       <c r="F27" s="54" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
     </row>
     <row r="28" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="55" t="s">
-        <v>291</v>
-      </c>
-      <c r="C28" s="117" t="s">
-        <v>292</v>
-      </c>
-      <c r="D28" s="117"/>
+        <v>283</v>
+      </c>
+      <c r="C28" s="125" t="s">
+        <v>284</v>
+      </c>
+      <c r="D28" s="125"/>
       <c r="E28" s="53"/>
       <c r="F28" s="54" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
     </row>
     <row r="29" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="52" t="s">
-        <v>294</v>
-      </c>
-      <c r="C29" s="118" t="s">
-        <v>295</v>
-      </c>
-      <c r="D29" s="118"/>
+        <v>286</v>
+      </c>
+      <c r="C29" s="126" t="s">
+        <v>287</v>
+      </c>
+      <c r="D29" s="126"/>
       <c r="E29" s="53"/>
       <c r="F29" s="54" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B21:E21"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="B23:F23"/>
@@ -7244,6 +7306,16 @@
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -7263,35 +7335,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="115" t="s">
-        <v>298</v>
-      </c>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
+      <c r="B1" s="116" t="s">
+        <v>290</v>
+      </c>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
     </row>
     <row r="2" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="121" t="s">
-        <v>299</v>
-      </c>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
+      <c r="B2" s="128" t="s">
+        <v>291</v>
+      </c>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="128"/>
     </row>
     <row r="3" spans="2:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="107" t="s">
-        <v>300</v>
-      </c>
-      <c r="C4" s="107"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="107"/>
+      <c r="B4" s="112" t="s">
+        <v>292</v>
+      </c>
+      <c r="C4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
     </row>
     <row r="5" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="2"/>
@@ -7304,13 +7376,13 @@
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="56"/>
       <c r="C6" s="56" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="D6" s="56"/>
       <c r="E6" s="56" t="s">
@@ -7321,33 +7393,33 @@
     </row>
     <row r="7" spans="2:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="107" t="s">
-        <v>302</v>
-      </c>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="107"/>
-      <c r="F8" s="107"/>
-      <c r="G8" s="107"/>
+      <c r="B8" s="112" t="s">
+        <v>294</v>
+      </c>
+      <c r="C8" s="112"/>
+      <c r="D8" s="112"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="112"/>
     </row>
     <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="18" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>256</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -7374,10 +7446,10 @@
     </row>
     <row r="11" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="33" t="s">
+        <v>261</v>
+      </c>
+      <c r="C11" s="49" t="s">
         <v>262</v>
-      </c>
-      <c r="C11" s="49" t="s">
-        <v>263</v>
       </c>
       <c r="D11" s="57">
         <v>4</v>
@@ -7396,10 +7468,10 @@
     </row>
     <row r="12" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="30" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C12" s="45" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D12" s="57">
         <v>5</v>
@@ -7418,7 +7490,7 @@
     </row>
     <row r="13" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="33" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C13" s="49" t="s">
         <v>260</v>
@@ -7440,7 +7512,7 @@
     </row>
     <row r="14" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="30" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C14" s="45" t="s">
         <v>260</v>
@@ -7462,7 +7534,7 @@
     </row>
     <row r="15" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="33" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C15" s="49" t="s">
         <v>260</v>
@@ -7484,10 +7556,10 @@
     </row>
     <row r="16" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="30" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C16" s="45" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="D16" s="57">
         <v>4</v>
@@ -7506,10 +7578,10 @@
     </row>
     <row r="17" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="C17" s="49" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D17" s="57">
         <v>5</v>
@@ -7530,21 +7602,21 @@
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="126" t="s">
-        <v>311</v>
-      </c>
-      <c r="C19" s="126"/>
+      <c r="B19" s="129" t="s">
+        <v>303</v>
+      </c>
+      <c r="C19" s="129"/>
       <c r="D19" s="51">
         <f>D10*0.15+D11*0.12+D12*0.1+D13*0.15+D14*0.15+D15*0.15+D16*0.08+D17*0.1</f>
         <v>4.4249999999999989</v>
@@ -7564,43 +7636,43 @@
     </row>
     <row r="20" spans="2:7" ht="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="21" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="107" t="s">
-        <v>312</v>
-      </c>
-      <c r="C21" s="107"/>
-      <c r="D21" s="107"/>
-      <c r="E21" s="107"/>
-      <c r="F21" s="107"/>
-      <c r="G21" s="107"/>
+      <c r="B21" s="112" t="s">
+        <v>304</v>
+      </c>
+      <c r="C21" s="112"/>
+      <c r="D21" s="112"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="112"/>
     </row>
     <row r="22" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="121" t="s">
-        <v>313</v>
-      </c>
-      <c r="C22" s="121"/>
-      <c r="D22" s="121"/>
-      <c r="E22" s="121"/>
-      <c r="F22" s="121"/>
-      <c r="G22" s="121"/>
+      <c r="B22" s="128" t="s">
+        <v>305</v>
+      </c>
+      <c r="C22" s="128"/>
+      <c r="D22" s="128"/>
+      <c r="E22" s="128"/>
+      <c r="F22" s="128"/>
+      <c r="G22" s="128"/>
     </row>
     <row r="23" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="1" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>256</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -7629,7 +7701,7 @@
     </row>
     <row r="25" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="33" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C25" s="66">
         <v>0.12</v>
@@ -7653,7 +7725,7 @@
     </row>
     <row r="26" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="30" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C26" s="62">
         <v>0.1</v>
@@ -7677,7 +7749,7 @@
     </row>
     <row r="27" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="33" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C27" s="66">
         <v>0.15</v>
@@ -7701,7 +7773,7 @@
     </row>
     <row r="28" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="30" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C28" s="62">
         <v>0.15</v>
@@ -7725,7 +7797,7 @@
     </row>
     <row r="29" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="33" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C29" s="66">
         <v>0.15</v>
@@ -7749,7 +7821,7 @@
     </row>
     <row r="30" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="30" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C30" s="62">
         <v>0.08</v>
@@ -7773,7 +7845,7 @@
     </row>
     <row r="31" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="33" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="C31" s="66">
         <v>0.1</v>
@@ -7797,339 +7869,317 @@
     </row>
     <row r="32" spans="2:7" ht="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="33" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="107" t="s">
-        <v>319</v>
-      </c>
-      <c r="C33" s="107"/>
-      <c r="D33" s="107"/>
-      <c r="E33" s="107"/>
-      <c r="F33" s="107"/>
-      <c r="G33" s="107"/>
+      <c r="B33" s="112" t="s">
+        <v>311</v>
+      </c>
+      <c r="C33" s="112"/>
+      <c r="D33" s="112"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="112"/>
     </row>
     <row r="34" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="125" t="s">
-        <v>644</v>
-      </c>
-      <c r="C34" s="125"/>
-      <c r="D34" s="125"/>
-      <c r="E34" s="125"/>
-      <c r="F34" s="125"/>
-      <c r="G34" s="125"/>
+      <c r="B34" s="130" t="s">
+        <v>636</v>
+      </c>
+      <c r="C34" s="130"/>
+      <c r="D34" s="130"/>
+      <c r="E34" s="130"/>
+      <c r="F34" s="130"/>
+      <c r="G34" s="130"/>
     </row>
     <row r="35" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="125"/>
-      <c r="C35" s="125"/>
-      <c r="D35" s="125"/>
-      <c r="E35" s="125"/>
-      <c r="F35" s="125"/>
-      <c r="G35" s="125"/>
+      <c r="B35" s="130"/>
+      <c r="C35" s="130"/>
+      <c r="D35" s="130"/>
+      <c r="E35" s="130"/>
+      <c r="F35" s="130"/>
+      <c r="G35" s="130"/>
     </row>
     <row r="36" spans="2:7" ht="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="37" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="107" t="s">
+      <c r="B37" s="112" t="s">
+        <v>312</v>
+      </c>
+      <c r="C37" s="112"/>
+      <c r="D37" s="112"/>
+      <c r="E37" s="112"/>
+      <c r="F37" s="112"/>
+      <c r="G37" s="112"/>
+    </row>
+    <row r="38" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="127" t="s">
+        <v>313</v>
+      </c>
+      <c r="C38" s="127"/>
+      <c r="D38" s="127"/>
+      <c r="E38" s="127" t="s">
+        <v>314</v>
+      </c>
+      <c r="F38" s="127"/>
+      <c r="G38" s="17" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="131" t="s">
+        <v>316</v>
+      </c>
+      <c r="C39" s="131"/>
+      <c r="D39" s="131"/>
+      <c r="E39" s="125" t="s">
+        <v>317</v>
+      </c>
+      <c r="F39" s="125"/>
+      <c r="G39" s="69" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="132" t="s">
+        <v>319</v>
+      </c>
+      <c r="C40" s="132"/>
+      <c r="D40" s="132"/>
+      <c r="E40" s="125" t="s">
         <v>320</v>
       </c>
-      <c r="C37" s="107"/>
-      <c r="D37" s="107"/>
-      <c r="E37" s="107"/>
-      <c r="F37" s="107"/>
-      <c r="G37" s="107"/>
-    </row>
-    <row r="38" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="119" t="s">
+      <c r="F40" s="125"/>
+      <c r="G40" s="69" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="131" t="s">
         <v>321</v>
       </c>
-      <c r="C38" s="119"/>
-      <c r="D38" s="119"/>
-      <c r="E38" s="119" t="s">
+      <c r="C41" s="131"/>
+      <c r="D41" s="131"/>
+      <c r="E41" s="125" t="s">
         <v>322</v>
       </c>
-      <c r="F38" s="119"/>
-      <c r="G38" s="17" t="s">
+      <c r="F41" s="125"/>
+      <c r="G41" s="69" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="39" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="123" t="s">
+    <row r="42" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="132" t="s">
         <v>324</v>
       </c>
-      <c r="C39" s="123"/>
-      <c r="D39" s="123"/>
-      <c r="E39" s="117" t="s">
+      <c r="C42" s="132"/>
+      <c r="D42" s="132"/>
+      <c r="E42" s="125" t="s">
         <v>325</v>
       </c>
-      <c r="F39" s="117"/>
-      <c r="G39" s="69" t="s">
+      <c r="F42" s="125"/>
+      <c r="G42" s="69" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="40" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="124" t="s">
+    <row r="43" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B43" s="131" t="s">
         <v>327</v>
       </c>
-      <c r="C40" s="124"/>
-      <c r="D40" s="124"/>
-      <c r="E40" s="117" t="s">
+      <c r="C43" s="131"/>
+      <c r="D43" s="131"/>
+      <c r="E43" s="125" t="s">
         <v>328</v>
       </c>
-      <c r="F40" s="117"/>
-      <c r="G40" s="69" t="s">
+      <c r="F43" s="125"/>
+      <c r="G43" s="69" t="s">
         <v>326</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="123" t="s">
-        <v>329</v>
-      </c>
-      <c r="C41" s="123"/>
-      <c r="D41" s="123"/>
-      <c r="E41" s="117" t="s">
-        <v>330</v>
-      </c>
-      <c r="F41" s="117"/>
-      <c r="G41" s="69" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="124" t="s">
-        <v>332</v>
-      </c>
-      <c r="C42" s="124"/>
-      <c r="D42" s="124"/>
-      <c r="E42" s="117" t="s">
-        <v>333</v>
-      </c>
-      <c r="F42" s="117"/>
-      <c r="G42" s="69" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="43" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="123" t="s">
-        <v>335</v>
-      </c>
-      <c r="C43" s="123"/>
-      <c r="D43" s="123"/>
-      <c r="E43" s="117" t="s">
-        <v>336</v>
-      </c>
-      <c r="F43" s="117"/>
-      <c r="G43" s="69" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="44" spans="2:7" ht="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="45" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="107" t="s">
-        <v>337</v>
-      </c>
-      <c r="C45" s="107"/>
-      <c r="D45" s="107"/>
-      <c r="E45" s="107"/>
-      <c r="F45" s="107"/>
-      <c r="G45" s="107"/>
+      <c r="B45" s="112" t="s">
+        <v>329</v>
+      </c>
+      <c r="C45" s="112"/>
+      <c r="D45" s="112"/>
+      <c r="E45" s="112"/>
+      <c r="F45" s="112"/>
+      <c r="G45" s="112"/>
     </row>
     <row r="46" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="107" t="s">
-        <v>338</v>
-      </c>
-      <c r="C46" s="107"/>
-      <c r="D46" s="107"/>
-      <c r="E46" s="107"/>
-      <c r="F46" s="107"/>
-      <c r="G46" s="107"/>
+      <c r="B46" s="112" t="s">
+        <v>330</v>
+      </c>
+      <c r="C46" s="112"/>
+      <c r="D46" s="112"/>
+      <c r="E46" s="112"/>
+      <c r="F46" s="112"/>
+      <c r="G46" s="112"/>
     </row>
     <row r="47" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="122" t="s">
-        <v>645</v>
-      </c>
-      <c r="C47" s="122"/>
-      <c r="D47" s="122"/>
-      <c r="E47" s="122"/>
-      <c r="F47" s="122"/>
-      <c r="G47" s="122"/>
+      <c r="B47" s="133" t="s">
+        <v>637</v>
+      </c>
+      <c r="C47" s="133"/>
+      <c r="D47" s="133"/>
+      <c r="E47" s="133"/>
+      <c r="F47" s="133"/>
+      <c r="G47" s="133"/>
     </row>
     <row r="48" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="122"/>
-      <c r="C48" s="122"/>
-      <c r="D48" s="122"/>
-      <c r="E48" s="122"/>
-      <c r="F48" s="122"/>
-      <c r="G48" s="122"/>
+      <c r="B48" s="133"/>
+      <c r="C48" s="133"/>
+      <c r="D48" s="133"/>
+      <c r="E48" s="133"/>
+      <c r="F48" s="133"/>
+      <c r="G48" s="133"/>
     </row>
     <row r="49" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="122"/>
-      <c r="C49" s="122"/>
-      <c r="D49" s="122"/>
-      <c r="E49" s="122"/>
-      <c r="F49" s="122"/>
-      <c r="G49" s="122"/>
+      <c r="B49" s="133"/>
+      <c r="C49" s="133"/>
+      <c r="D49" s="133"/>
+      <c r="E49" s="133"/>
+      <c r="F49" s="133"/>
+      <c r="G49" s="133"/>
     </row>
     <row r="50" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="122"/>
-      <c r="C50" s="122"/>
-      <c r="D50" s="122"/>
-      <c r="E50" s="122"/>
-      <c r="F50" s="122"/>
-      <c r="G50" s="122"/>
+      <c r="B50" s="133"/>
+      <c r="C50" s="133"/>
+      <c r="D50" s="133"/>
+      <c r="E50" s="133"/>
+      <c r="F50" s="133"/>
+      <c r="G50" s="133"/>
     </row>
     <row r="51" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="107" t="s">
-        <v>339</v>
-      </c>
-      <c r="C51" s="107"/>
-      <c r="D51" s="107"/>
-      <c r="E51" s="107"/>
-      <c r="F51" s="107"/>
-      <c r="G51" s="107"/>
+      <c r="B51" s="112" t="s">
+        <v>331</v>
+      </c>
+      <c r="C51" s="112"/>
+      <c r="D51" s="112"/>
+      <c r="E51" s="112"/>
+      <c r="F51" s="112"/>
+      <c r="G51" s="112"/>
     </row>
     <row r="52" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="122" t="s">
-        <v>646</v>
-      </c>
-      <c r="C52" s="122"/>
-      <c r="D52" s="122"/>
-      <c r="E52" s="122"/>
-      <c r="F52" s="122"/>
-      <c r="G52" s="122"/>
+      <c r="B52" s="133" t="s">
+        <v>638</v>
+      </c>
+      <c r="C52" s="133"/>
+      <c r="D52" s="133"/>
+      <c r="E52" s="133"/>
+      <c r="F52" s="133"/>
+      <c r="G52" s="133"/>
     </row>
     <row r="53" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="122"/>
-      <c r="C53" s="122"/>
-      <c r="D53" s="122"/>
-      <c r="E53" s="122"/>
-      <c r="F53" s="122"/>
-      <c r="G53" s="122"/>
+      <c r="B53" s="133"/>
+      <c r="C53" s="133"/>
+      <c r="D53" s="133"/>
+      <c r="E53" s="133"/>
+      <c r="F53" s="133"/>
+      <c r="G53" s="133"/>
     </row>
     <row r="54" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="122"/>
-      <c r="C54" s="122"/>
-      <c r="D54" s="122"/>
-      <c r="E54" s="122"/>
-      <c r="F54" s="122"/>
-      <c r="G54" s="122"/>
+      <c r="B54" s="133"/>
+      <c r="C54" s="133"/>
+      <c r="D54" s="133"/>
+      <c r="E54" s="133"/>
+      <c r="F54" s="133"/>
+      <c r="G54" s="133"/>
     </row>
     <row r="55" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="122"/>
-      <c r="C55" s="122"/>
-      <c r="D55" s="122"/>
-      <c r="E55" s="122"/>
-      <c r="F55" s="122"/>
-      <c r="G55" s="122"/>
+      <c r="B55" s="133"/>
+      <c r="C55" s="133"/>
+      <c r="D55" s="133"/>
+      <c r="E55" s="133"/>
+      <c r="F55" s="133"/>
+      <c r="G55" s="133"/>
     </row>
     <row r="56" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B56" s="107" t="s">
-        <v>340</v>
-      </c>
-      <c r="C56" s="107"/>
-      <c r="D56" s="107"/>
-      <c r="E56" s="107"/>
-      <c r="F56" s="107"/>
-      <c r="G56" s="107"/>
+      <c r="B56" s="112" t="s">
+        <v>332</v>
+      </c>
+      <c r="C56" s="112"/>
+      <c r="D56" s="112"/>
+      <c r="E56" s="112"/>
+      <c r="F56" s="112"/>
+      <c r="G56" s="112"/>
     </row>
     <row r="57" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="122" t="s">
-        <v>647</v>
-      </c>
-      <c r="C57" s="122"/>
-      <c r="D57" s="122"/>
-      <c r="E57" s="122"/>
-      <c r="F57" s="122"/>
-      <c r="G57" s="122"/>
+      <c r="B57" s="133" t="s">
+        <v>639</v>
+      </c>
+      <c r="C57" s="133"/>
+      <c r="D57" s="133"/>
+      <c r="E57" s="133"/>
+      <c r="F57" s="133"/>
+      <c r="G57" s="133"/>
     </row>
     <row r="58" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B58" s="122"/>
-      <c r="C58" s="122"/>
-      <c r="D58" s="122"/>
-      <c r="E58" s="122"/>
-      <c r="F58" s="122"/>
-      <c r="G58" s="122"/>
+      <c r="B58" s="133"/>
+      <c r="C58" s="133"/>
+      <c r="D58" s="133"/>
+      <c r="E58" s="133"/>
+      <c r="F58" s="133"/>
+      <c r="G58" s="133"/>
     </row>
     <row r="59" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B59" s="122"/>
-      <c r="C59" s="122"/>
-      <c r="D59" s="122"/>
-      <c r="E59" s="122"/>
-      <c r="F59" s="122"/>
-      <c r="G59" s="122"/>
+      <c r="B59" s="133"/>
+      <c r="C59" s="133"/>
+      <c r="D59" s="133"/>
+      <c r="E59" s="133"/>
+      <c r="F59" s="133"/>
+      <c r="G59" s="133"/>
     </row>
     <row r="60" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B60" s="122"/>
-      <c r="C60" s="122"/>
-      <c r="D60" s="122"/>
-      <c r="E60" s="122"/>
-      <c r="F60" s="122"/>
-      <c r="G60" s="122"/>
+      <c r="B60" s="133"/>
+      <c r="C60" s="133"/>
+      <c r="D60" s="133"/>
+      <c r="E60" s="133"/>
+      <c r="F60" s="133"/>
+      <c r="G60" s="133"/>
     </row>
     <row r="61" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B61" s="107" t="s">
-        <v>341</v>
-      </c>
-      <c r="C61" s="107"/>
-      <c r="D61" s="107"/>
-      <c r="E61" s="107"/>
-      <c r="F61" s="107"/>
-      <c r="G61" s="107"/>
+      <c r="B61" s="112" t="s">
+        <v>333</v>
+      </c>
+      <c r="C61" s="112"/>
+      <c r="D61" s="112"/>
+      <c r="E61" s="112"/>
+      <c r="F61" s="112"/>
+      <c r="G61" s="112"/>
     </row>
     <row r="62" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="122" t="s">
-        <v>648</v>
-      </c>
-      <c r="C62" s="122"/>
-      <c r="D62" s="122"/>
-      <c r="E62" s="122"/>
-      <c r="F62" s="122"/>
-      <c r="G62" s="122"/>
+      <c r="B62" s="133" t="s">
+        <v>640</v>
+      </c>
+      <c r="C62" s="133"/>
+      <c r="D62" s="133"/>
+      <c r="E62" s="133"/>
+      <c r="F62" s="133"/>
+      <c r="G62" s="133"/>
     </row>
     <row r="63" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="122"/>
-      <c r="C63" s="122"/>
-      <c r="D63" s="122"/>
-      <c r="E63" s="122"/>
-      <c r="F63" s="122"/>
-      <c r="G63" s="122"/>
+      <c r="B63" s="133"/>
+      <c r="C63" s="133"/>
+      <c r="D63" s="133"/>
+      <c r="E63" s="133"/>
+      <c r="F63" s="133"/>
+      <c r="G63" s="133"/>
     </row>
     <row r="64" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="122"/>
-      <c r="C64" s="122"/>
-      <c r="D64" s="122"/>
-      <c r="E64" s="122"/>
-      <c r="F64" s="122"/>
-      <c r="G64" s="122"/>
+      <c r="B64" s="133"/>
+      <c r="C64" s="133"/>
+      <c r="D64" s="133"/>
+      <c r="E64" s="133"/>
+      <c r="F64" s="133"/>
+      <c r="G64" s="133"/>
     </row>
     <row r="65" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="122"/>
-      <c r="C65" s="122"/>
-      <c r="D65" s="122"/>
-      <c r="E65" s="122"/>
-      <c r="F65" s="122"/>
-      <c r="G65" s="122"/>
+      <c r="B65" s="133"/>
+      <c r="C65" s="133"/>
+      <c r="D65" s="133"/>
+      <c r="E65" s="133"/>
+      <c r="F65" s="133"/>
+      <c r="G65" s="133"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="B34:G35"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="E43:F43"/>
     <mergeCell ref="B56:G56"/>
     <mergeCell ref="B57:G60"/>
     <mergeCell ref="B61:G61"/>
@@ -8139,6 +8189,28 @@
     <mergeCell ref="B47:G50"/>
     <mergeCell ref="B51:G51"/>
     <mergeCell ref="B52:G55"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B34:G35"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="B19:C19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -8159,557 +8231,621 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="115" t="s">
-        <v>342</v>
-      </c>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
+      <c r="B1" s="116" t="s">
+        <v>334</v>
+      </c>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
     </row>
     <row r="2" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="121" t="s">
-        <v>343</v>
-      </c>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
+      <c r="B2" s="128" t="s">
+        <v>335</v>
+      </c>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
     </row>
     <row r="3" spans="2:6" ht="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="107" t="s">
-        <v>344</v>
-      </c>
-      <c r="C4" s="107"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
+      <c r="B4" s="112" t="s">
+        <v>336</v>
+      </c>
+      <c r="C4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
     </row>
     <row r="5" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="127" t="s">
-        <v>345</v>
-      </c>
-      <c r="C5" s="127"/>
-      <c r="D5" s="127"/>
-      <c r="E5" s="127"/>
-      <c r="F5" s="127"/>
+      <c r="B5" s="134" t="s">
+        <v>337</v>
+      </c>
+      <c r="C5" s="134"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
     </row>
     <row r="6" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="127"/>
-      <c r="C6" s="127"/>
-      <c r="D6" s="127"/>
-      <c r="E6" s="127"/>
-      <c r="F6" s="127"/>
+      <c r="B6" s="134"/>
+      <c r="C6" s="134"/>
+      <c r="D6" s="134"/>
+      <c r="E6" s="134"/>
+      <c r="F6" s="134"/>
     </row>
     <row r="7" spans="2:6" ht="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="8" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="107" t="s">
-        <v>346</v>
-      </c>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="107"/>
-      <c r="F8" s="107"/>
+      <c r="B8" s="112" t="s">
+        <v>338</v>
+      </c>
+      <c r="C8" s="112"/>
+      <c r="D8" s="112"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
     </row>
     <row r="9" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="70" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="C9" s="70" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="D9" s="70" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="E9" s="70" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="F9" s="70" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="28" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="C10" s="71" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="D10" s="71" t="s">
         <v>17</v>
       </c>
       <c r="E10" s="71" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="F10" s="71" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="28" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="C11" s="71" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="D11" s="71" t="s">
         <v>18</v>
       </c>
       <c r="E11" s="71" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="F11" s="71" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="21" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="C12" s="72" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="D12" s="72" t="s">
         <v>18</v>
       </c>
       <c r="E12" s="72" t="s">
+        <v>346</v>
+      </c>
+      <c r="F12" s="72" t="s">
         <v>354</v>
-      </c>
-      <c r="F12" s="72" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="14" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="107" t="s">
-        <v>363</v>
-      </c>
-      <c r="C14" s="107"/>
-      <c r="D14" s="107"/>
-      <c r="E14" s="107"/>
-      <c r="F14" s="107"/>
+      <c r="B14" s="112" t="s">
+        <v>355</v>
+      </c>
+      <c r="C14" s="112"/>
+      <c r="D14" s="112"/>
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
     </row>
     <row r="15" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="109" t="s">
-        <v>364</v>
-      </c>
-      <c r="C15" s="109"/>
-      <c r="D15" s="109"/>
-      <c r="E15" s="109"/>
-      <c r="F15" s="109"/>
+      <c r="B15" s="114" t="s">
+        <v>356</v>
+      </c>
+      <c r="C15" s="114"/>
+      <c r="D15" s="114"/>
+      <c r="E15" s="114"/>
+      <c r="F15" s="114"/>
     </row>
     <row r="16" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="109" t="s">
-        <v>365</v>
-      </c>
-      <c r="D16" s="109"/>
-      <c r="E16" s="109"/>
-      <c r="F16" s="109"/>
+      <c r="C16" s="114" t="s">
+        <v>357</v>
+      </c>
+      <c r="D16" s="114"/>
+      <c r="E16" s="114"/>
+      <c r="F16" s="114"/>
     </row>
     <row r="17" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="114"/>
-      <c r="D17" s="114"/>
-      <c r="E17" s="114"/>
-      <c r="F17" s="114"/>
+      <c r="C17" s="118" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="118"/>
+      <c r="E17" s="118"/>
+      <c r="F17" s="118"/>
     </row>
     <row r="18" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="C18" s="114"/>
-      <c r="D18" s="114"/>
-      <c r="E18" s="114"/>
-      <c r="F18" s="114"/>
+        <v>358</v>
+      </c>
+      <c r="C18" s="118" t="s">
+        <v>657</v>
+      </c>
+      <c r="D18" s="118"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="118"/>
     </row>
     <row r="19" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="C19" s="114"/>
-      <c r="D19" s="114"/>
-      <c r="E19" s="114"/>
-      <c r="F19" s="114"/>
+        <v>359</v>
+      </c>
+      <c r="C19" s="118" t="s">
+        <v>504</v>
+      </c>
+      <c r="D19" s="118"/>
+      <c r="E19" s="118"/>
+      <c r="F19" s="118"/>
     </row>
     <row r="20" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="C20" s="114"/>
-      <c r="D20" s="114"/>
-      <c r="E20" s="114"/>
-      <c r="F20" s="114"/>
+        <v>360</v>
+      </c>
+      <c r="C20" s="118">
+        <v>4</v>
+      </c>
+      <c r="D20" s="118"/>
+      <c r="E20" s="118"/>
+      <c r="F20" s="118"/>
     </row>
     <row r="21" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="C21" s="114"/>
-      <c r="D21" s="114"/>
-      <c r="E21" s="114"/>
-      <c r="F21" s="114"/>
+        <v>361</v>
+      </c>
+      <c r="C21" s="118">
+        <v>5</v>
+      </c>
+      <c r="D21" s="118"/>
+      <c r="E21" s="118"/>
+      <c r="F21" s="118"/>
     </row>
     <row r="22" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="C22" s="114"/>
-      <c r="D22" s="114"/>
-      <c r="E22" s="114"/>
-      <c r="F22" s="114"/>
+        <v>362</v>
+      </c>
+      <c r="C22" s="118" t="s">
+        <v>658</v>
+      </c>
+      <c r="D22" s="118"/>
+      <c r="E22" s="118"/>
+      <c r="F22" s="118"/>
     </row>
     <row r="23" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="C23" s="114"/>
-      <c r="D23" s="114"/>
-      <c r="E23" s="114"/>
-      <c r="F23" s="114"/>
+        <v>363</v>
+      </c>
+      <c r="C23" s="118" t="s">
+        <v>659</v>
+      </c>
+      <c r="D23" s="118"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="118"/>
     </row>
     <row r="24" spans="2:6" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="C24" s="114"/>
-      <c r="D24" s="114"/>
-      <c r="E24" s="114"/>
-      <c r="F24" s="114"/>
+        <v>364</v>
+      </c>
+      <c r="C24" s="118" t="s">
+        <v>660</v>
+      </c>
+      <c r="D24" s="118"/>
+      <c r="E24" s="118"/>
+      <c r="F24" s="118"/>
     </row>
     <row r="25" spans="2:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="27" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="109" t="s">
-        <v>373</v>
-      </c>
-      <c r="C27" s="109"/>
-      <c r="D27" s="109"/>
-      <c r="E27" s="109"/>
-      <c r="F27" s="109"/>
+      <c r="B27" s="114" t="s">
+        <v>365</v>
+      </c>
+      <c r="C27" s="114"/>
+      <c r="D27" s="114"/>
+      <c r="E27" s="114"/>
+      <c r="F27" s="114"/>
     </row>
     <row r="28" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="109" t="s">
-        <v>365</v>
-      </c>
-      <c r="D28" s="109"/>
-      <c r="E28" s="109"/>
-      <c r="F28" s="109"/>
+      <c r="C28" s="114" t="s">
+        <v>357</v>
+      </c>
+      <c r="D28" s="114"/>
+      <c r="E28" s="114"/>
+      <c r="F28" s="114"/>
     </row>
     <row r="29" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C29" s="114"/>
-      <c r="D29" s="114"/>
-      <c r="E29" s="114"/>
-      <c r="F29" s="114"/>
+      <c r="C29" s="118" t="s">
+        <v>29</v>
+      </c>
+      <c r="D29" s="118"/>
+      <c r="E29" s="118"/>
+      <c r="F29" s="118"/>
     </row>
     <row r="30" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="C30" s="114"/>
-      <c r="D30" s="114"/>
-      <c r="E30" s="114"/>
-      <c r="F30" s="114"/>
+        <v>358</v>
+      </c>
+      <c r="C30" s="118" t="s">
+        <v>661</v>
+      </c>
+      <c r="D30" s="118"/>
+      <c r="E30" s="118"/>
+      <c r="F30" s="118"/>
     </row>
     <row r="31" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="C31" s="114"/>
-      <c r="D31" s="114"/>
-      <c r="E31" s="114"/>
-      <c r="F31" s="114"/>
+        <v>359</v>
+      </c>
+      <c r="C31" s="118" t="s">
+        <v>346</v>
+      </c>
+      <c r="D31" s="118"/>
+      <c r="E31" s="118"/>
+      <c r="F31" s="118"/>
     </row>
     <row r="32" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="C32" s="114"/>
-      <c r="D32" s="114"/>
-      <c r="E32" s="114"/>
-      <c r="F32" s="114"/>
+        <v>360</v>
+      </c>
+      <c r="C32" s="118">
+        <v>4</v>
+      </c>
+      <c r="D32" s="118"/>
+      <c r="E32" s="118"/>
+      <c r="F32" s="118"/>
     </row>
     <row r="33" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="C33" s="114"/>
-      <c r="D33" s="114"/>
-      <c r="E33" s="114"/>
-      <c r="F33" s="114"/>
+        <v>361</v>
+      </c>
+      <c r="C33" s="118">
+        <v>5</v>
+      </c>
+      <c r="D33" s="118"/>
+      <c r="E33" s="118"/>
+      <c r="F33" s="118"/>
     </row>
     <row r="34" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B34" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="C34" s="114"/>
-      <c r="D34" s="114"/>
-      <c r="E34" s="114"/>
-      <c r="F34" s="114"/>
+        <v>362</v>
+      </c>
+      <c r="C34" s="118" t="s">
+        <v>662</v>
+      </c>
+      <c r="D34" s="118"/>
+      <c r="E34" s="118"/>
+      <c r="F34" s="118"/>
     </row>
     <row r="35" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="C35" s="114"/>
-      <c r="D35" s="114"/>
-      <c r="E35" s="114"/>
-      <c r="F35" s="114"/>
+        <v>363</v>
+      </c>
+      <c r="C35" s="118" t="s">
+        <v>663</v>
+      </c>
+      <c r="D35" s="118"/>
+      <c r="E35" s="118"/>
+      <c r="F35" s="118"/>
     </row>
     <row r="36" spans="2:6" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="C36" s="114"/>
-      <c r="D36" s="114"/>
-      <c r="E36" s="114"/>
-      <c r="F36" s="114"/>
+        <v>364</v>
+      </c>
+      <c r="C36" s="118" t="s">
+        <v>664</v>
+      </c>
+      <c r="D36" s="118"/>
+      <c r="E36" s="118"/>
+      <c r="F36" s="118"/>
     </row>
     <row r="37" spans="2:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="39" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="119" t="s">
-        <v>374</v>
-      </c>
-      <c r="C39" s="119"/>
-      <c r="D39" s="119"/>
-      <c r="E39" s="119"/>
-      <c r="F39" s="119"/>
+      <c r="B39" s="127" t="s">
+        <v>366</v>
+      </c>
+      <c r="C39" s="127"/>
+      <c r="D39" s="127"/>
+      <c r="E39" s="127"/>
+      <c r="F39" s="127"/>
     </row>
     <row r="40" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="119" t="s">
-        <v>365</v>
-      </c>
-      <c r="D40" s="119"/>
-      <c r="E40" s="119"/>
-      <c r="F40" s="119"/>
+      <c r="C40" s="127" t="s">
+        <v>357</v>
+      </c>
+      <c r="D40" s="127"/>
+      <c r="E40" s="127"/>
+      <c r="F40" s="127"/>
     </row>
     <row r="41" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B41" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C41" s="114"/>
-      <c r="D41" s="114"/>
-      <c r="E41" s="114"/>
-      <c r="F41" s="114"/>
+      <c r="C41" s="123" t="s">
+        <v>30</v>
+      </c>
+      <c r="D41" s="118"/>
+      <c r="E41" s="118"/>
+      <c r="F41" s="118"/>
     </row>
     <row r="42" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B42" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="C42" s="114"/>
-      <c r="D42" s="114"/>
-      <c r="E42" s="114"/>
-      <c r="F42" s="114"/>
+        <v>358</v>
+      </c>
+      <c r="C42" s="123" t="s">
+        <v>665</v>
+      </c>
+      <c r="D42" s="118"/>
+      <c r="E42" s="118"/>
+      <c r="F42" s="118"/>
     </row>
     <row r="43" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B43" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="C43" s="114"/>
-      <c r="D43" s="114"/>
-      <c r="E43" s="114"/>
-      <c r="F43" s="114"/>
+        <v>359</v>
+      </c>
+      <c r="C43" s="123" t="s">
+        <v>508</v>
+      </c>
+      <c r="D43" s="118"/>
+      <c r="E43" s="118"/>
+      <c r="F43" s="118"/>
     </row>
     <row r="44" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B44" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="C44" s="114"/>
-      <c r="D44" s="114"/>
-      <c r="E44" s="114"/>
-      <c r="F44" s="114"/>
+        <v>360</v>
+      </c>
+      <c r="C44" s="118">
+        <v>3.5</v>
+      </c>
+      <c r="D44" s="118"/>
+      <c r="E44" s="118"/>
+      <c r="F44" s="118"/>
     </row>
     <row r="45" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="C45" s="114"/>
-      <c r="D45" s="114"/>
-      <c r="E45" s="114"/>
-      <c r="F45" s="114"/>
+        <v>361</v>
+      </c>
+      <c r="C45" s="118">
+        <v>5</v>
+      </c>
+      <c r="D45" s="118"/>
+      <c r="E45" s="118"/>
+      <c r="F45" s="118"/>
     </row>
     <row r="46" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="C46" s="114"/>
-      <c r="D46" s="114"/>
-      <c r="E46" s="114"/>
-      <c r="F46" s="114"/>
+        <v>362</v>
+      </c>
+      <c r="C46" s="123" t="s">
+        <v>666</v>
+      </c>
+      <c r="D46" s="118"/>
+      <c r="E46" s="118"/>
+      <c r="F46" s="118"/>
     </row>
     <row r="47" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B47" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="C47" s="114"/>
-      <c r="D47" s="114"/>
-      <c r="E47" s="114"/>
-      <c r="F47" s="114"/>
+        <v>363</v>
+      </c>
+      <c r="C47" s="123" t="s">
+        <v>667</v>
+      </c>
+      <c r="D47" s="118"/>
+      <c r="E47" s="118"/>
+      <c r="F47" s="118"/>
     </row>
     <row r="48" spans="2:6" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B48" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="C48" s="114"/>
-      <c r="D48" s="114"/>
-      <c r="E48" s="114"/>
-      <c r="F48" s="114"/>
+        <v>364</v>
+      </c>
+      <c r="C48" s="123" t="s">
+        <v>668</v>
+      </c>
+      <c r="D48" s="118"/>
+      <c r="E48" s="118"/>
+      <c r="F48" s="118"/>
     </row>
     <row r="49" spans="2:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="51" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="119" t="s">
-        <v>375</v>
-      </c>
-      <c r="C51" s="119"/>
-      <c r="D51" s="119"/>
-      <c r="E51" s="119"/>
-      <c r="F51" s="119"/>
+      <c r="B51" s="127" t="s">
+        <v>367</v>
+      </c>
+      <c r="C51" s="127"/>
+      <c r="D51" s="127"/>
+      <c r="E51" s="127"/>
+      <c r="F51" s="127"/>
     </row>
     <row r="52" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B52" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C52" s="119" t="s">
-        <v>365</v>
-      </c>
-      <c r="D52" s="119"/>
-      <c r="E52" s="119"/>
-      <c r="F52" s="119"/>
+      <c r="C52" s="127" t="s">
+        <v>357</v>
+      </c>
+      <c r="D52" s="127"/>
+      <c r="E52" s="127"/>
+      <c r="F52" s="127"/>
     </row>
     <row r="53" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C53" s="114"/>
-      <c r="D53" s="114"/>
-      <c r="E53" s="114"/>
-      <c r="F53" s="114"/>
+      <c r="C53" s="123" t="s">
+        <v>30</v>
+      </c>
+      <c r="D53" s="118"/>
+      <c r="E53" s="118"/>
+      <c r="F53" s="118"/>
     </row>
     <row r="54" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="C54" s="114"/>
-      <c r="D54" s="114"/>
-      <c r="E54" s="114"/>
-      <c r="F54" s="114"/>
+        <v>358</v>
+      </c>
+      <c r="C54" s="123" t="s">
+        <v>669</v>
+      </c>
+      <c r="D54" s="118"/>
+      <c r="E54" s="118"/>
+      <c r="F54" s="118"/>
     </row>
     <row r="55" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="C55" s="114"/>
-      <c r="D55" s="114"/>
-      <c r="E55" s="114"/>
-      <c r="F55" s="114"/>
+        <v>359</v>
+      </c>
+      <c r="C55" s="123" t="s">
+        <v>522</v>
+      </c>
+      <c r="D55" s="118"/>
+      <c r="E55" s="118"/>
+      <c r="F55" s="118"/>
     </row>
     <row r="56" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B56" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="C56" s="114"/>
-      <c r="D56" s="114"/>
-      <c r="E56" s="114"/>
-      <c r="F56" s="114"/>
+        <v>360</v>
+      </c>
+      <c r="C56" s="118">
+        <v>3</v>
+      </c>
+      <c r="D56" s="118"/>
+      <c r="E56" s="118"/>
+      <c r="F56" s="118"/>
     </row>
     <row r="57" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B57" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="C57" s="114"/>
-      <c r="D57" s="114"/>
-      <c r="E57" s="114"/>
-      <c r="F57" s="114"/>
+        <v>361</v>
+      </c>
+      <c r="C57" s="118">
+        <v>5</v>
+      </c>
+      <c r="D57" s="118"/>
+      <c r="E57" s="118"/>
+      <c r="F57" s="118"/>
     </row>
     <row r="58" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="C58" s="114"/>
-      <c r="D58" s="114"/>
-      <c r="E58" s="114"/>
-      <c r="F58" s="114"/>
+        <v>362</v>
+      </c>
+      <c r="C58" s="123" t="s">
+        <v>670</v>
+      </c>
+      <c r="D58" s="118"/>
+      <c r="E58" s="118"/>
+      <c r="F58" s="118"/>
     </row>
     <row r="59" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B59" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="C59" s="114"/>
-      <c r="D59" s="114"/>
-      <c r="E59" s="114"/>
-      <c r="F59" s="114"/>
+        <v>363</v>
+      </c>
+      <c r="C59" s="123" t="s">
+        <v>671</v>
+      </c>
+      <c r="D59" s="118"/>
+      <c r="E59" s="118"/>
+      <c r="F59" s="118"/>
     </row>
     <row r="60" spans="2:6" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B60" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="C60" s="114"/>
-      <c r="D60" s="114"/>
-      <c r="E60" s="114"/>
-      <c r="F60" s="114"/>
+        <v>364</v>
+      </c>
+      <c r="C60" s="123" t="s">
+        <v>672</v>
+      </c>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
     </row>
     <row r="61" spans="2:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B5:F6"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="C40:F40"/>
-    <mergeCell ref="C41:F41"/>
-    <mergeCell ref="C42:F42"/>
-    <mergeCell ref="C43:F43"/>
-    <mergeCell ref="C44:F44"/>
-    <mergeCell ref="C45:F45"/>
-    <mergeCell ref="C46:F46"/>
-    <mergeCell ref="C47:F47"/>
-    <mergeCell ref="C48:F48"/>
-    <mergeCell ref="B51:F51"/>
-    <mergeCell ref="C52:F52"/>
-    <mergeCell ref="C53:F53"/>
-    <mergeCell ref="C54:F54"/>
     <mergeCell ref="C60:F60"/>
     <mergeCell ref="C55:F55"/>
     <mergeCell ref="C56:F56"/>
     <mergeCell ref="C57:F57"/>
     <mergeCell ref="C58:F58"/>
     <mergeCell ref="C59:F59"/>
+    <mergeCell ref="C48:F48"/>
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="C52:F52"/>
+    <mergeCell ref="C53:F53"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="C43:F43"/>
+    <mergeCell ref="C44:F44"/>
+    <mergeCell ref="C45:F45"/>
+    <mergeCell ref="C46:F46"/>
+    <mergeCell ref="C47:F47"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="C41:F41"/>
+    <mergeCell ref="C42:F42"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F6"/>
+    <mergeCell ref="B8:F8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -8730,34 +8866,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="115" t="s">
-        <v>376</v>
-      </c>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
+      <c r="B1" s="116" t="s">
+        <v>368</v>
+      </c>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
     </row>
     <row r="2" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="116" t="s">
-        <v>377</v>
-      </c>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
+      <c r="B2" s="117" t="s">
+        <v>369</v>
+      </c>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
     </row>
     <row r="3" spans="2:5" ht="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="18" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
@@ -8765,13 +8901,13 @@
         <v>57</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
@@ -8779,13 +8915,13 @@
         <v>60</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
     </row>
     <row r="7" spans="2:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
@@ -8793,13 +8929,13 @@
         <v>62</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
     </row>
     <row r="8" spans="2:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
@@ -8807,13 +8943,13 @@
         <v>64</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9" spans="2:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
@@ -8821,13 +8957,13 @@
         <v>67</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
     </row>
     <row r="10" spans="2:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
@@ -8835,146 +8971,146 @@
         <v>69</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
     </row>
     <row r="11" spans="2:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="22" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
     </row>
     <row r="12" spans="2:5" ht="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="13" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="107" t="s">
-        <v>401</v>
-      </c>
-      <c r="C13" s="107"/>
-      <c r="D13" s="107"/>
-      <c r="E13" s="107"/>
+      <c r="B13" s="112" t="s">
+        <v>393</v>
+      </c>
+      <c r="C13" s="112"/>
+      <c r="D13" s="112"/>
+      <c r="E13" s="112"/>
     </row>
     <row r="14" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="70" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="C14" s="70" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="D14" s="70" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="E14" s="70"/>
     </row>
     <row r="15" spans="2:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="73" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>406</v>
-      </c>
-      <c r="D15" s="128" t="s">
-        <v>407</v>
-      </c>
-      <c r="E15" s="128"/>
+        <v>398</v>
+      </c>
+      <c r="D15" s="135" t="s">
+        <v>399</v>
+      </c>
+      <c r="E15" s="135"/>
     </row>
     <row r="16" spans="2:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="73" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>409</v>
-      </c>
-      <c r="D16" s="128" t="s">
-        <v>410</v>
-      </c>
-      <c r="E16" s="128"/>
+        <v>401</v>
+      </c>
+      <c r="D16" s="135" t="s">
+        <v>402</v>
+      </c>
+      <c r="E16" s="135"/>
     </row>
     <row r="17" spans="2:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="73" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>412</v>
-      </c>
-      <c r="D17" s="128" t="s">
-        <v>413</v>
-      </c>
-      <c r="E17" s="128"/>
+        <v>404</v>
+      </c>
+      <c r="D17" s="135" t="s">
+        <v>405</v>
+      </c>
+      <c r="E17" s="135"/>
     </row>
     <row r="18" spans="2:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="73" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>415</v>
-      </c>
-      <c r="D18" s="128" t="s">
-        <v>416</v>
-      </c>
-      <c r="E18" s="128"/>
+        <v>407</v>
+      </c>
+      <c r="D18" s="135" t="s">
+        <v>408</v>
+      </c>
+      <c r="E18" s="135"/>
     </row>
     <row r="19" spans="2:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="73" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="C19" s="31" t="s">
-        <v>418</v>
-      </c>
-      <c r="D19" s="128" t="s">
-        <v>419</v>
-      </c>
-      <c r="E19" s="128"/>
+        <v>410</v>
+      </c>
+      <c r="D19" s="135" t="s">
+        <v>411</v>
+      </c>
+      <c r="E19" s="135"/>
     </row>
     <row r="20" spans="2:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="73" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>421</v>
-      </c>
-      <c r="D20" s="128" t="s">
-        <v>422</v>
-      </c>
-      <c r="E20" s="128"/>
+        <v>413</v>
+      </c>
+      <c r="D20" s="135" t="s">
+        <v>414</v>
+      </c>
+      <c r="E20" s="135"/>
     </row>
     <row r="21" spans="2:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="73" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>424</v>
-      </c>
-      <c r="D21" s="128" t="s">
-        <v>425</v>
-      </c>
-      <c r="E21" s="128"/>
+        <v>416</v>
+      </c>
+      <c r="D21" s="135" t="s">
+        <v>417</v>
+      </c>
+      <c r="E21" s="135"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D21:E21"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:E21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -8994,231 +9130,231 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="115" t="s">
-        <v>426</v>
-      </c>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
+      <c r="B1" s="116" t="s">
+        <v>418</v>
+      </c>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
     </row>
     <row r="2" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="116" t="s">
-        <v>427</v>
-      </c>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
+      <c r="B2" s="117" t="s">
+        <v>419</v>
+      </c>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="117"/>
     </row>
     <row r="3" spans="2:7" ht="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="107" t="s">
-        <v>428</v>
-      </c>
-      <c r="C4" s="107"/>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="107"/>
+      <c r="B4" s="112" t="s">
+        <v>420</v>
+      </c>
+      <c r="C4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
     </row>
     <row r="5" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="18" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="D5" s="18" t="s">
         <v>256</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
     </row>
     <row r="6" spans="2:7" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="22" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="C6" s="22">
         <v>3</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
     </row>
     <row r="7" spans="2:7" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="21" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="C7" s="21">
         <v>3</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="G7" s="29" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="24" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="C8" s="24">
         <v>2</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="74" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="C9" s="74">
         <v>3</v>
       </c>
       <c r="D9" s="74" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="30" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="C10" s="30">
         <v>2</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="33" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="C11" s="33">
         <v>1</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="22" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="C12" s="22">
         <v>1</v>
       </c>
       <c r="D12" s="22" t="s">
+        <v>449</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>454</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>455</v>
+      </c>
+      <c r="G12" s="29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="136" t="s">
         <v>457</v>
       </c>
-      <c r="E12" s="20" t="s">
-        <v>462</v>
-      </c>
-      <c r="F12" s="25" t="s">
-        <v>463</v>
-      </c>
-      <c r="G12" s="29" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="135" t="s">
-        <v>465</v>
-      </c>
-      <c r="C13" s="135"/>
-      <c r="D13" s="135"/>
+      <c r="C13" s="136"/>
+      <c r="D13" s="136"/>
       <c r="E13" s="75">
         <f>SUM(C6:C12)</f>
         <v>15</v>
       </c>
-      <c r="F13" s="135" t="s">
-        <v>466</v>
-      </c>
-      <c r="G13" s="135"/>
+      <c r="F13" s="136" t="s">
+        <v>458</v>
+      </c>
+      <c r="G13" s="136"/>
     </row>
     <row r="14" spans="2:7" ht="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="15" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="107" t="s">
-        <v>467</v>
-      </c>
-      <c r="C15" s="107"/>
-      <c r="D15" s="107"/>
-      <c r="E15" s="107"/>
-      <c r="F15" s="107"/>
-      <c r="G15" s="107"/>
+      <c r="B15" s="112" t="s">
+        <v>459</v>
+      </c>
+      <c r="C15" s="112"/>
+      <c r="D15" s="112"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="112"/>
     </row>
     <row r="16" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="18" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="E16" s="18"/>
       <c r="F16" s="18"/>
@@ -9226,110 +9362,110 @@
     </row>
     <row r="17" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="76" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>471</v>
-      </c>
-      <c r="D17" s="131" t="s">
-        <v>472</v>
-      </c>
-      <c r="E17" s="131"/>
-      <c r="F17" s="131"/>
-      <c r="G17" s="131"/>
+        <v>463</v>
+      </c>
+      <c r="D17" s="137" t="s">
+        <v>464</v>
+      </c>
+      <c r="E17" s="137"/>
+      <c r="F17" s="137"/>
+      <c r="G17" s="137"/>
     </row>
     <row r="18" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="77" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>474</v>
-      </c>
-      <c r="D18" s="132" t="s">
-        <v>475</v>
-      </c>
-      <c r="E18" s="132"/>
-      <c r="F18" s="132"/>
-      <c r="G18" s="132"/>
+        <v>466</v>
+      </c>
+      <c r="D18" s="138" t="s">
+        <v>467</v>
+      </c>
+      <c r="E18" s="138"/>
+      <c r="F18" s="138"/>
+      <c r="G18" s="138"/>
     </row>
     <row r="19" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="78" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>477</v>
-      </c>
-      <c r="D19" s="133" t="s">
-        <v>478</v>
-      </c>
-      <c r="E19" s="133"/>
-      <c r="F19" s="133"/>
-      <c r="G19" s="133"/>
+        <v>469</v>
+      </c>
+      <c r="D19" s="139" t="s">
+        <v>470</v>
+      </c>
+      <c r="E19" s="139"/>
+      <c r="F19" s="139"/>
+      <c r="G19" s="139"/>
     </row>
     <row r="20" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="79" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>480</v>
-      </c>
-      <c r="D20" s="134" t="s">
-        <v>481</v>
-      </c>
-      <c r="E20" s="134"/>
-      <c r="F20" s="134"/>
-      <c r="G20" s="134"/>
+        <v>472</v>
+      </c>
+      <c r="D20" s="140" t="s">
+        <v>473</v>
+      </c>
+      <c r="E20" s="140"/>
+      <c r="F20" s="140"/>
+      <c r="G20" s="140"/>
     </row>
     <row r="21" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="80" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>483</v>
-      </c>
-      <c r="D21" s="129" t="s">
-        <v>484</v>
-      </c>
-      <c r="E21" s="129"/>
-      <c r="F21" s="129"/>
-      <c r="G21" s="129"/>
+        <v>475</v>
+      </c>
+      <c r="D21" s="141" t="s">
+        <v>476</v>
+      </c>
+      <c r="E21" s="141"/>
+      <c r="F21" s="141"/>
+      <c r="G21" s="141"/>
     </row>
     <row r="22" spans="2:7" ht="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="23" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="107" t="s">
-        <v>485</v>
-      </c>
-      <c r="C23" s="107"/>
-      <c r="D23" s="107"/>
-      <c r="E23" s="107"/>
-      <c r="F23" s="107"/>
-      <c r="G23" s="107"/>
+      <c r="B23" s="112" t="s">
+        <v>477</v>
+      </c>
+      <c r="C23" s="112"/>
+      <c r="D23" s="112"/>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="112"/>
     </row>
     <row r="24" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="C24" s="130" t="s">
+      <c r="C24" s="142" t="s">
         <v>189</v>
       </c>
-      <c r="D24" s="130"/>
+      <c r="D24" s="142"/>
       <c r="E24" s="18"/>
       <c r="F24" s="18" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
     </row>
     <row r="25" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="52" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="118" t="s">
-        <v>487</v>
-      </c>
-      <c r="D25" s="118"/>
-      <c r="E25" s="118"/>
+      <c r="C25" s="126" t="s">
+        <v>479</v>
+      </c>
+      <c r="D25" s="126"/>
+      <c r="E25" s="126"/>
       <c r="F25" s="53"/>
       <c r="G25" s="53"/>
     </row>
@@ -9337,11 +9473,11 @@
       <c r="B26" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="C26" s="117" t="s">
-        <v>488</v>
-      </c>
-      <c r="D26" s="117"/>
-      <c r="E26" s="117"/>
+      <c r="C26" s="125" t="s">
+        <v>480</v>
+      </c>
+      <c r="D26" s="125"/>
+      <c r="E26" s="125"/>
       <c r="F26" s="53"/>
       <c r="G26" s="53"/>
     </row>
@@ -9349,11 +9485,11 @@
       <c r="B27" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="118" t="s">
-        <v>489</v>
-      </c>
-      <c r="D27" s="118"/>
-      <c r="E27" s="118"/>
+      <c r="C27" s="126" t="s">
+        <v>481</v>
+      </c>
+      <c r="D27" s="126"/>
+      <c r="E27" s="126"/>
       <c r="F27" s="53"/>
       <c r="G27" s="53"/>
     </row>
@@ -9361,11 +9497,11 @@
       <c r="B28" s="55" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="117" t="s">
-        <v>490</v>
-      </c>
-      <c r="D28" s="117"/>
-      <c r="E28" s="117"/>
+      <c r="C28" s="125" t="s">
+        <v>482</v>
+      </c>
+      <c r="D28" s="125"/>
+      <c r="E28" s="125"/>
       <c r="F28" s="53"/>
       <c r="G28" s="53"/>
     </row>
@@ -9373,11 +9509,11 @@
       <c r="B29" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="118" t="s">
-        <v>491</v>
-      </c>
-      <c r="D29" s="118"/>
-      <c r="E29" s="118"/>
+      <c r="C29" s="126" t="s">
+        <v>483</v>
+      </c>
+      <c r="D29" s="126"/>
+      <c r="E29" s="126"/>
       <c r="F29" s="53"/>
       <c r="G29" s="53"/>
     </row>
@@ -9385,113 +9521,113 @@
       <c r="B30" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="C30" s="117" t="s">
-        <v>492</v>
-      </c>
-      <c r="D30" s="117"/>
-      <c r="E30" s="117"/>
+      <c r="C30" s="125" t="s">
+        <v>484</v>
+      </c>
+      <c r="D30" s="125"/>
+      <c r="E30" s="125"/>
       <c r="F30" s="53"/>
       <c r="G30" s="53"/>
     </row>
     <row r="31" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="52" t="s">
-        <v>399</v>
-      </c>
-      <c r="C31" s="118" t="s">
-        <v>493</v>
-      </c>
-      <c r="D31" s="118"/>
-      <c r="E31" s="118"/>
+        <v>391</v>
+      </c>
+      <c r="C31" s="126" t="s">
+        <v>485</v>
+      </c>
+      <c r="D31" s="126"/>
+      <c r="E31" s="126"/>
       <c r="F31" s="53"/>
       <c r="G31" s="53"/>
     </row>
     <row r="32" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="55" t="s">
-        <v>494</v>
-      </c>
-      <c r="C32" s="117" t="s">
-        <v>495</v>
-      </c>
-      <c r="D32" s="117"/>
-      <c r="E32" s="117"/>
+        <v>486</v>
+      </c>
+      <c r="C32" s="125" t="s">
+        <v>487</v>
+      </c>
+      <c r="D32" s="125"/>
+      <c r="E32" s="125"/>
       <c r="F32" s="53"/>
       <c r="G32" s="53"/>
     </row>
     <row r="33" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="52" t="s">
-        <v>496</v>
-      </c>
-      <c r="C33" s="118" t="s">
-        <v>497</v>
-      </c>
-      <c r="D33" s="118"/>
-      <c r="E33" s="118"/>
+        <v>488</v>
+      </c>
+      <c r="C33" s="126" t="s">
+        <v>489</v>
+      </c>
+      <c r="D33" s="126"/>
+      <c r="E33" s="126"/>
       <c r="F33" s="53"/>
       <c r="G33" s="53"/>
     </row>
     <row r="34" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B34" s="55" t="s">
-        <v>498</v>
-      </c>
-      <c r="C34" s="117" t="s">
-        <v>499</v>
-      </c>
-      <c r="D34" s="117"/>
-      <c r="E34" s="117"/>
+        <v>490</v>
+      </c>
+      <c r="C34" s="125" t="s">
+        <v>491</v>
+      </c>
+      <c r="D34" s="125"/>
+      <c r="E34" s="125"/>
       <c r="F34" s="53"/>
       <c r="G34" s="53"/>
     </row>
     <row r="35" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="52" t="s">
-        <v>500</v>
-      </c>
-      <c r="C35" s="118" t="s">
-        <v>501</v>
-      </c>
-      <c r="D35" s="118"/>
-      <c r="E35" s="118"/>
+        <v>492</v>
+      </c>
+      <c r="C35" s="126" t="s">
+        <v>493</v>
+      </c>
+      <c r="D35" s="126"/>
+      <c r="E35" s="126"/>
       <c r="F35" s="53"/>
       <c r="G35" s="53"/>
     </row>
     <row r="36" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="55" t="s">
-        <v>502</v>
-      </c>
-      <c r="C36" s="117" t="s">
-        <v>503</v>
-      </c>
-      <c r="D36" s="117"/>
-      <c r="E36" s="117"/>
+        <v>494</v>
+      </c>
+      <c r="C36" s="125" t="s">
+        <v>495</v>
+      </c>
+      <c r="D36" s="125"/>
+      <c r="E36" s="125"/>
       <c r="F36" s="53"/>
       <c r="G36" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="D20:G20"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B4:G4"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="F13:G13"/>
-    <mergeCell ref="B15:G15"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="C36:E36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
